--- a/workspaces/btc_daily_14days/volatility/vol_ratio_7_21.xlsx
+++ b/workspaces/btc_daily_14days/volatility/vol_ratio_7_21.xlsx
@@ -575,46 +575,46 @@
         <v>57</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1381406271576466</v>
+        <v>0.1374673263503041</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14.31959598277268</v>
+        <v>14.2733772859875</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.662323505394788</v>
+        <v>8.634312351291619</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.06191227715396</v>
+        <v>14.0164679486201</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15.28261956384299</v>
+        <v>15.23312307268503</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>17.34069684599777</v>
+        <v>17.28485126629987</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22.53110665307427</v>
+        <v>22.45859980583625</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>22.06876169243713</v>
+        <v>21.9976272953928</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>18.4974160346085</v>
+        <v>18.4377309301541</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>14.13347735776311</v>
+        <v>14.08770618779374</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>15.6906043819165</v>
+        <v>15.63966763031769</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>17.48826919306927</v>
+        <v>17.4314499683767</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>17.07125730478662</v>
+        <v>17.01566006593432</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>19.0860840458585</v>
+        <v>19.02404407380267</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>68</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.022850084915184</v>
+        <v>-1.019734262610875</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.661680562788597</v>
+        <v>7.635854585862717</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.268566906104425</v>
+        <v>7.244246093210108</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.400851494033873</v>
+        <v>7.375834645710988</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.391791014562756</v>
+        <v>5.373194222910463</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.635856046180947</v>
+        <v>8.606817392241815</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17.39021653387473</v>
+        <v>17.3322939369884</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>15.45353265433291</v>
+        <v>15.40186459858233</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>15.39633666884811</v>
+        <v>15.34494578143335</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>14.54821639772406</v>
+        <v>14.49963962215909</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.87254887112454</v>
+        <v>12.82925353020205</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>18.80924434014572</v>
+        <v>18.74629659235298</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>13.96749867507749</v>
+        <v>13.9203334501947</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.74628523500475</v>
+        <v>12.70309464139827</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>88</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-9.311620138392051</v>
+        <v>-9.280556968042013</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.105983685824299</v>
+        <v>-4.093350901368289</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.04573644154802281</v>
+        <v>0.04467995843162953</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.587970168358424</v>
+        <v>3.574743877458396</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.325107704060436</v>
+        <v>5.305985682234912</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.348731627111327</v>
+        <v>3.336269938686847</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.12700605530776</v>
+        <v>2.117982454318138</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.755594631369782</v>
+        <v>-1.751580157294143</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.955805385914111</v>
+        <v>-2.947665969099766</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.3915628942452116</v>
+        <v>-0.391949854729269</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.736021194464989</v>
+        <v>-1.732025717501799</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.701409580813667</v>
+        <v>-1.698047322845291</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-8.962756758490428</v>
+        <v>-8.934854711089855</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.574192922988871</v>
+        <v>-7.550916053787724</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>103</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.846367505032738</v>
+        <v>2.837080337497</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>7.061977949874851</v>
+        <v>7.036740538195325</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.811906702670477</v>
+        <v>1.804706452531704</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.9713029455654336</v>
+        <v>0.9664295597928998</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.348463012114799</v>
+        <v>3.335188224991512</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.535904608688853</v>
+        <v>7.50837304460017</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.591327607186244</v>
+        <v>2.580245733526787</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.069321408945093</v>
+        <v>4.053453351461805</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6.928109731511213</v>
+        <v>6.90257905073485</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.02439354197017</v>
+        <v>7.994966437421255</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.821389675176022</v>
+        <v>7.792630986301631</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.016266252242858</v>
+        <v>2.006979280886441</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.464567305324906</v>
+        <v>6.440685288594075</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.742834548808005</v>
+        <v>5.721369912672927</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>104</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.352715525943658</v>
+        <v>1.348200598464821</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.435602478137554</v>
+        <v>7.407615131082366</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.194351529079114</v>
+        <v>3.181842431553662</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.250446992125703</v>
+        <v>5.230124161874571</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.750551336410545</v>
+        <v>3.735101145809402</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.012523203041241</v>
+        <v>4.992385235381924</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.076815035567847</v>
+        <v>1.070478037954501</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.572504606233075</v>
+        <v>1.564594522164043</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.415257968375748</v>
+        <v>-0.4161899232439836</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.588374746883197</v>
+        <v>2.576562708808758</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.312320037340704</v>
+        <v>4.294381003866093</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.454906085484652</v>
+        <v>1.447085365927535</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.06884993782825433</v>
+        <v>0.06629927633841959</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.540178887397538</v>
+        <v>-3.529937032809649</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.73044227680478</v>
+        <v>2.784195935269025</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.46751727820881</v>
+        <v>-1.483256733409355</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.7078419250476102</v>
+        <v>-0.7133343101969558</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.32912837934375</v>
+        <v>-1.34285067358023</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3678728473168889</v>
+        <v>-0.3606285349556302</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.810407283544379</v>
+        <v>-3.870079606111695</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.893897177541518</v>
+        <v>-3.956571461451674</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.9588875171935243</v>
+        <v>-0.963637980640506</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.718713235841662</v>
+        <v>2.786813890278083</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.3585853337057756</v>
+        <v>-0.3490124805436849</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.683154161102216</v>
+        <v>1.734629250067016</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.272726236254577</v>
+        <v>-1.281920854933851</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.310777883538961</v>
+        <v>1.350419529953328</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.558141178380723</v>
+        <v>1.600714758147916</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.645980693091076</v>
+        <v>-1.660294203497983</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.257554306055589</v>
+        <v>-3.281058232455393</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.432322750059683</v>
+        <v>1.449050691786674</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.9585965577196802</v>
+        <v>-0.9616753245214937</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.494914957835839</v>
+        <v>-1.501688141647264</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.8943181994214697</v>
+        <v>-0.8959412207107817</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.4121154307068124</v>
+        <v>-0.4100421295350998</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.005666443241715</v>
+        <v>-2.017327498123755</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.325382439581347</v>
+        <v>1.344678975414418</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4840877411742213</v>
+        <v>0.4961644987121261</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.8462604820859312</v>
+        <v>0.8627962703366947</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.014660497799376</v>
+        <v>2.04000069479784</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.731889494571583</v>
+        <v>2.76324919621279</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.414947314144435</v>
+        <v>2.442590439718252</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.254203870449217</v>
+        <v>-2.260066352844639</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.951901885327239</v>
+        <v>-1.955601745173446</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4328949938378059</v>
+        <v>-0.4326690481982496</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.259579660273367</v>
+        <v>-1.261278287312955</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.810630395464393</v>
+        <v>1.817098183225049</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.542052469730649</v>
+        <v>3.552975208648384</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.937895026031505</v>
+        <v>3.9497056094825</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.994222769264823</v>
+        <v>3.003580554828446</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.933456824512838</v>
+        <v>2.943387210426899</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.003528837144202</v>
+        <v>4.016207150225213</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.237741398304784</v>
+        <v>5.254001541830895</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.357554565722594</v>
+        <v>3.368617756134171</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.501773516948589</v>
+        <v>1.508026641561209</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3133212071882241</v>
+        <v>0.3162168133446244</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.573547325722934</v>
+        <v>1.591960712728124</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.473432985805928</v>
+        <v>-1.487347772872106</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4328949938378059</v>
+        <v>-0.4316600840505984</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3026418612304127</v>
+        <v>-0.2993120151971311</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.190345372953196</v>
+        <v>-4.234096462555684</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.371372334759073</v>
+        <v>-4.415983450820605</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.328182181073387</v>
+        <v>-1.333045181771276</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.5995652361286332</v>
+        <v>0.6191455820310097</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3175234879193454</v>
+        <v>0.3373166795588389</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.262832195078154</v>
+        <v>-0.2497750068607729</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.467895862401484</v>
+        <v>-0.4542337058267947</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.964103002947589</v>
+        <v>2.006201503606505</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.8423942100873489</v>
+        <v>-0.8391169188856722</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1140652652172705</v>
+        <v>-0.1038728057740101</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>209</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.254203870449217</v>
+        <v>-2.250785372100687</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.736590880542657</v>
+        <v>-6.727215629114902</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-10.95921078331138</v>
+        <v>-10.94392344788352</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-7.001206454531527</v>
+        <v>-6.991781278838836</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-7.539627669603917</v>
+        <v>-7.529503554202734</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-6.285247932845081</v>
+        <v>-6.27712604322533</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-5.891512750595936</v>
+        <v>-5.88424220107224</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.444820551291429</v>
+        <v>-4.439757179794398</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.419696035559738</v>
+        <v>-6.412175864711564</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.877476722979786</v>
+        <v>-4.872266206281139</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-6.04080372387255</v>
+        <v>-6.034260213744631</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.529301372351064</v>
+        <v>-5.523330206596434</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.161939933509046</v>
+        <v>-1.161861895768091</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.349630247417487</v>
+        <v>-2.347566771491692</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>190</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3881751623152425</v>
+        <v>-0.3871601840579899</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.31604069840472</v>
+        <v>4.309470401764891</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.8156701134551554</v>
+        <v>-0.8139661176032149</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-6.474890665058176</v>
+        <v>-6.46481325061719</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.539627669603917</v>
+        <v>-7.527911937951735</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-7.242185731888256</v>
+        <v>-7.231278820537128</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-5.747972080739473</v>
+        <v>-5.739784751633096</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.688839690047175</v>
+        <v>-5.681019674821997</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.216706587076558</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-5.02101739283659</v>
+        <v>-5.014761502283335</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-4.700820013811835</v>
+        <v>-4.695359669286177</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-6.248040468583739</v>
+        <v>-6.239997808928237</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.036159955090135</v>
+        <v>-4.031539751413284</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.206187905980514</v>
+        <v>-2.204026101635129</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>223</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>5.802525805350562</v>
+        <v>5.793025181944628</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.845660712565575</v>
+        <v>2.840458877018854</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6570700328749197</v>
+        <v>0.6565333331337371</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.029475631850133</v>
+        <v>3.024928643257425</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1995285428633906</v>
+        <v>-0.1984053811181496</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.09791339485227013</v>
+        <v>0.09808344135738167</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.471125255155336</v>
+        <v>-4.463683507207257</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.247725694295788</v>
+        <v>-2.2444563441654</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.654017060298507</v>
+        <v>-3.648695551089439</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.813559285685287</v>
+        <v>-1.811729377693752</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.81325980761531</v>
+        <v>-3.808358909541589</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.536166968355481</v>
+        <v>-1.534830950412093</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.855167455027917</v>
+        <v>-2.851763590824966</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.953751727114977</v>
+        <v>-3.948184704420122</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.517256866955805</v>
+        <v>1.534443025791262</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.768113537452187</v>
+        <v>-2.790923636137279</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.836779035492867</v>
+        <v>-5.897455629138598</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.032729111441391</v>
+        <v>-3.064058260364156</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.432112893358365</v>
+        <v>-1.451294423319105</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.204189672220366</v>
+        <v>-2.22795417787048</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.358442106070299</v>
+        <v>-3.394030780111969</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-5.964662938006526</v>
+        <v>-6.021770186271937</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4.956144107611649</v>
+        <v>-5.002279092509234</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.528194426329051</v>
+        <v>-1.536829645433869</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.9009971500248781</v>
+        <v>-0.9029432497376249</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.56940926290757</v>
+        <v>1.591673696936752</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.154444295440527</v>
+        <v>1.17268539528007</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.011059495492816</v>
+        <v>3.044907042034858</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>195</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.23702806379972</v>
+        <v>-2.23510540327441</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7667829386206435</v>
+        <v>0.7657292278984045</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.910375770485587</v>
+        <v>1.909286154807305</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.066269928734229</v>
+        <v>3.063535666599513</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>7.65605384186707</v>
+        <v>7.648840187132556</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>6.415034241121198</v>
+        <v>6.408828917234125</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>7.355941549490055</v>
+        <v>7.348918141154293</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>5.350296612246787</v>
+        <v>5.345108096766083</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.864549427781327</v>
+        <v>-0.8635166616166785</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.875068976933882</v>
+        <v>1.87253343875706</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.20877719107807</v>
+        <v>3.204747109108048</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>5.807262912526177</v>
+        <v>5.800336746779521</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5.390240693971627</v>
+        <v>5.38377590919081</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>5.643316731453126</v>
+        <v>5.636729633857563</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>191</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.527504088166985</v>
+        <v>3.523234488450498</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.8688100563545618</v>
+        <v>0.8674057218811058</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.521061768606259</v>
+        <v>1.520177684702773</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.154967821299508</v>
+        <v>-5.148869103918621</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-6.216949245795647</v>
+        <v>-6.209833660893189</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.254585842111453</v>
+        <v>-2.252212529290254</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.815759349959656</v>
+        <v>-1.813808954517491</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.282942748741156</v>
+        <v>-2.280517193184856</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.296822216075462</v>
+        <v>-1.295064310234359</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.9944138554414153</v>
+        <v>0.9923275666942075</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7810200971485344</v>
+        <v>-0.781362473644343</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.871164107317313</v>
+        <v>1.867222268569634</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.166706944911077</v>
+        <v>-1.167076156584947</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.6558309448810888</v>
+        <v>0.6535104098004041</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>215</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.06470121467374668</v>
+        <v>0.06383184302686828</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.081756119220749</v>
+        <v>-1.080979070226483</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.08127598860802721</v>
+        <v>-0.08029645925043383</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.514093423069184</v>
+        <v>0.5143885757924096</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.419676629212283</v>
+        <v>-1.416952411541381</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.517583528705877</v>
+        <v>-2.514234734300722</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.6534967075102145</v>
+        <v>0.6527315485546623</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.581662145938012</v>
+        <v>1.579670914177058</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4.311359934174376</v>
+        <v>4.306239873722504</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.189928041551276</v>
+        <v>-1.189708075836933</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.650495319357233</v>
+        <v>-4.645860652246597</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-6.941693557360637</v>
+        <v>-6.935140747255851</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-6.900353043797622</v>
+        <v>-6.893310734673811</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-6.653746811840087</v>
+        <v>-6.647110556959539</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>191</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.184537796649764</v>
+        <v>-1.183801245292351</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.392370265778652</v>
+        <v>1.389679671899842</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.521061768606138</v>
+        <v>1.519940260093179</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6041944823654717</v>
+        <v>0.6044444478784783</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>5.301375361534141</v>
+        <v>5.294865992672783</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.981016252129386</v>
+        <v>2.977151282288226</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.419842744281191</v>
+        <v>3.414703822893351</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.429099136075607</v>
+        <v>2.425234166234446</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.7732620066512013</v>
+        <v>-0.7723263041251585</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.099826982255045</v>
+        <v>-1.099675052497631</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.351700725420848</v>
+        <v>-2.349098928325823</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.793757358651277</v>
+        <v>-1.792919691880883</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.215096246879213</v>
+        <v>-2.212927692313208</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1314547266301744</v>
+        <v>0.1299502003765056</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.311295407600745</v>
+        <v>4.336408687940484</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.108005818305053</v>
+        <v>2.122105688602616</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.06201081728561775</v>
+        <v>-0.06571051142671536</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.115189637340833</v>
+        <v>-1.1249134525941</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.837042805075797</v>
+        <v>-2.853171758083306</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.13131684369143</v>
+        <v>-3.147409724117502</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.62433458463228</v>
+        <v>-2.635129304649119</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.316370054419764</v>
+        <v>-1.320414692621583</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.152517869596082</v>
+        <v>-3.168265805961433</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.635779149298635</v>
+        <v>-1.639097826797517</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.432248449947508</v>
+        <v>-2.442770371066651</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6227173636080607</v>
+        <v>-0.6200119199947807</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.325507108102343</v>
+        <v>1.335102030573687</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.4649827220790428</v>
+        <v>-0.4621714650436459</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>181</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.76968141413272</v>
+        <v>-2.768228011056344</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.486227402787492</v>
+        <v>-5.481741395208331</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-5.881096109384082</v>
+        <v>-5.874350532965437</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.883439661859455</v>
+        <v>-1.880442588188338</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.421860876931561</v>
+        <v>-2.418603083779061</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.124418939215964</v>
+        <v>-2.121769491520183</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.209152656488307</v>
+        <v>-2.207111554249259</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-4.886280806650952</v>
+        <v>-4.881737661653247</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.947280692833388</v>
+        <v>-4.941868482897291</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.034974938634669</v>
+        <v>-3.032798915264401</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.134755887261697</v>
+        <v>-2.132657647604049</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.9954003542256658</v>
+        <v>-0.9956394671202489</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.416247132846202</v>
+        <v>-1.415654965170496</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.493137878015105</v>
+        <v>0.4915249306416314</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.202764211435635</v>
+        <v>3.230001945419708</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.57336636355398</v>
+        <v>-1.581788719003896</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.72796746149497</v>
+        <v>3.739031002197592</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.32657502448221</v>
+        <v>1.324743366597993</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-5.540960114640555</v>
+        <v>-5.585042559524403</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.446049822494551</v>
+        <v>-1.461422665451593</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.8978721473617313</v>
+        <v>-0.9046918021629011</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.799501415882091</v>
+        <v>1.808316269450081</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.371412922104952</v>
+        <v>2.377799193567377</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.276180617353461</v>
+        <v>-2.287522177556333</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.6836230203543465</v>
+        <v>0.6859780090626018</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.079462176730601</v>
+        <v>-3.09095910077199</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-5.044406114926069</v>
+        <v>-5.071917061802765</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-7.965024691407748</v>
+        <v>-8.00690910532262</v>
       </c>
     </row>
     <row r="26">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 0.3553</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4073~4086</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4073</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.07053083122319492</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 0.3985</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4016~4029</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4016</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.0734829963082646</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 0.4418</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3948~3961</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3948</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.05718484886435959</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 0.4851</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3860~3873</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3860</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.1530889196557581</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 0.5283</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3757~3770</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3757</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.07950597687224814</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 0.5716</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3653~3666</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3653</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.04338655704043504</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 0.6149</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3522~3532</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3522</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.05855723300724947</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 0.6581</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3347~3355</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3347</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.02519059186155204</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 0.7014</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3139~3146</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3139</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.1766188953017789</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 0.7447</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2933~2937</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2933</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.07721200324933619</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 0.7879</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2724~2728</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2724</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.2558285419601134</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 0.8312</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2534~2538</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2534</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.3040400091832467</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.8745</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2311~2315</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2311</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.225619745695937</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.9177</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2126~2128</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2126</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.3787766660746357</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.961</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1931~1933</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1931</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.1913172648556056</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 1.004</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1740~1742</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1740</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.5990640377759888</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 1.048</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1525~1527</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1525</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.6925214898235978</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 1.091</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1334~1336</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1334</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.622180835180032</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 1.134</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1166~1167</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1166</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.33662598087836</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 1.177</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>985~986</t>
-        </is>
+      <c r="B25" t="n">
+        <v>985</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.073560024063923</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 1.221</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>828~828</t>
-        </is>
+      <c r="B26" t="n">
+        <v>828</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.889573585910455</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 1.264</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>721~721</t>
-        </is>
+      <c r="B27" t="n">
+        <v>721</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-2.146697682207204</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 1.307</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>578~578</t>
-        </is>
+      <c r="B28" t="n">
+        <v>578</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-1.10935527522728</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 1.35</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>458~458</t>
-        </is>
+      <c r="B29" t="n">
+        <v>458</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-1.401735263441417</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 1.394</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>382~382</t>
-        </is>
+      <c r="B30" t="n">
+        <v>382</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.1374173778015972</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 1.437</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>299~299</t>
-        </is>
+      <c r="B31" t="n">
+        <v>299</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.6539734372668349</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 1.48</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>229~229</t>
-        </is>
+      <c r="B32" t="n">
+        <v>229</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-1.838416486148844</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 1.523</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>174~174</t>
-        </is>
+      <c r="B33" t="n">
+        <v>174</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-1.344013032853653</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 1.567</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>135~135</t>
-        </is>
+      <c r="B34" t="n">
+        <v>135</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-4.34529017206183</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 1.61</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-6.064866891638545</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 0.3553</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>3.458942632170981</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 0.3985</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>141~141</t>
-        </is>
+      <c r="B7" t="n">
+        <v>141</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>2.116490757804208</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 0.4418</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>209~209</t>
-        </is>
+      <c r="B8" t="n">
+        <v>209</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>1.095078426201511</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 0.4851</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>297~297</t>
-        </is>
+      <c r="B9" t="n">
+        <v>297</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-1.98838781515947</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 0.5283</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>400~400</t>
-        </is>
+      <c r="B10" t="n">
+        <v>400</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.7434383202099824</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 0.5716</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>504~504</t>
-        </is>
+      <c r="B11" t="n">
+        <v>504</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.3108986376702916</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 0.6149</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>635~638</t>
-        </is>
+      <c r="B12" t="n">
+        <v>635</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.3278782942100946</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 0.6581</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>810~815</t>
-        </is>
+      <c r="B13" t="n">
+        <v>810</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.1008002834001616</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 0.7014</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1018~1024</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1018</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.5403133202099752</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 0.7447</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1224~1233</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1224</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.1820027970956204</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 0.7879</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1433~1442</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1433</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.48234261979389</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 0.8312</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1623~1632</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1623</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.4713794966805622</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.8745</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1846~1855</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1846</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.2828420032401553</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.9177</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2031~2042</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2031</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.3958858717586793</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.961</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2226~2237</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2226</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.1663739283371939</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 1.004</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2417~2428</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2417</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.4307791427224785</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 1.048</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2632~2643</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2632</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.4009998182690282</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 1.091</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2823~2834</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2823</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.2941410728740053</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 1.134</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2991~3003</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2991</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.5202146934430445</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 1.177</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3172~3184</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3172</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.3331948456191753</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 1.221</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3329~3342</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3329</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.4688597049246681</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 1.264</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3436~3449</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3436</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.4494436745711212</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 1.307</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3579~3592</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3579</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.1791674704358996</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 1.35</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3699~3712</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3699</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.1735875418589856</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 1.394</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3775~3788</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3775</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.01448142635813809</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 1.437</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3858~3871</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3858</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.05112380843895892</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 1.48</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3928~3941</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3928</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.1074244049866735</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 1.523</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3983~3996</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3983</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.05911423234257995</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 1.567</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4022~4035</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4022</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.1459668842509885</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 1.61</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4073~4086</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4073</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.1252596729373607</v>

--- a/workspaces/btc_daily_14days/volatility/vol_ratio_7_21.xlsx
+++ b/workspaces/btc_daily_14days/volatility/vol_ratio_7_21.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that VOL Ratio-7-21 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that VOL Ratio-7-21 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>57</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1374673263503041</v>
+        <v>0.1499484065002648</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14.2733772859875</v>
+        <v>14.28625824928604</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.634312351291619</v>
+        <v>8.647288945656328</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.0164679486201</v>
+        <v>14.02942272635277</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15.23312307268503</v>
+        <v>15.24621235739014</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>17.28485126629987</v>
+        <v>17.29787609425895</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22.45859980583625</v>
+        <v>22.47165242269371</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>21.9976272953928</v>
+        <v>22.01079629293246</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>18.4377309301541</v>
+        <v>18.45091854623199</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>14.08770618779374</v>
+        <v>14.10110115215043</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>15.63966763031769</v>
+        <v>15.65311756421488</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>17.4314499683767</v>
+        <v>17.44489758013518</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>17.01566006593432</v>
+        <v>17.02921372566014</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>19.02404407380267</v>
+        <v>19.01361443810452</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>68</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.019734262610875</v>
+        <v>-1.007255438975726</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.635854585862717</v>
+        <v>7.64872988648866</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.244246093210108</v>
+        <v>7.257220935117523</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.375834645710988</v>
+        <v>7.388784685118942</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.373194222910463</v>
+        <v>5.386277423216391</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.606817392241815</v>
+        <v>8.619837480469471</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17.3322939369884</v>
+        <v>17.34534413783669</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>15.40186459858233</v>
+        <v>15.41503094481205</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>15.34494578143335</v>
+        <v>15.35813223907923</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>14.49963962215909</v>
+        <v>14.51303448351733</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.82925353020205</v>
+        <v>12.84270278510594</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>18.74629659235298</v>
+        <v>18.75974429477953</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>13.9203334501947</v>
+        <v>13.93388687018641</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.70309464139827</v>
+        <v>12.69266500570144</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>88</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-9.280556968042013</v>
+        <v>-9.268087108797587</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.093350901368289</v>
+        <v>-4.080486156845438</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.04467995843162953</v>
+        <v>0.05764841542979582</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.574743877458396</v>
+        <v>3.587690401048484</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.305985682234912</v>
+        <v>5.319067863775999</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.336269938686847</v>
+        <v>3.349286470630965</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.117982454318138</v>
+        <v>2.131025200520966</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.751580157294143</v>
+        <v>-1.738421048475779</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.947665969099766</v>
+        <v>-2.93448592949818</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.391949854729269</v>
+        <v>-0.3785592441306278</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.732025717501799</v>
+        <v>-1.718579611488494</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.698047322845291</v>
+        <v>-1.684602446459451</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-8.934854711089855</v>
+        <v>-8.921302892369859</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.550916053787724</v>
+        <v>-7.561345689486387</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>103</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.837080337497</v>
+        <v>2.849558241324758</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>7.036740538195325</v>
+        <v>7.049612272022713</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.804706452531704</v>
+        <v>1.817674328941862</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.9664295597928998</v>
+        <v>0.9793727247037012</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.335188224991512</v>
+        <v>3.348267880638488</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.50837304460017</v>
+        <v>7.5213907019223</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.580245733526787</v>
+        <v>2.593287581523477</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.053453351461805</v>
+        <v>4.066613786943606</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6.90257905073485</v>
+        <v>6.915761582620732</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.994966437421255</v>
+        <v>8.008358686158473</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.792630986301631</v>
+        <v>7.806078533899296</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.006979280886441</v>
+        <v>2.020424298303261</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.440685288594075</v>
+        <v>6.454237952194916</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.721369912672927</v>
+        <v>5.710940276974327</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>104</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.348200598464821</v>
+        <v>1.360674695336272</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.407615131082366</v>
+        <v>7.420485407387673</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.181842431553662</v>
+        <v>3.19480931650736</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.230124161874571</v>
+        <v>5.243068537715402</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.735101145809402</v>
+        <v>3.748179452360802</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.992385235381924</v>
+        <v>5.005400223569445</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.070478037954501</v>
+        <v>1.08351780809393</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.564594522164043</v>
+        <v>1.57775279051782</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.4161899232439836</v>
+        <v>-0.4030108939307482</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.576562708808758</v>
+        <v>2.589952747060352</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.294381003866093</v>
+        <v>4.307827317040179</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.447085365927535</v>
+        <v>1.46052990994761</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.06629927633841959</v>
+        <v>0.07985129941909719</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.529937032809649</v>
+        <v>-3.540366668507367</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>131</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.784195935269025</v>
+        <v>2.79700704467384</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.483256733409355</v>
+        <v>-1.877058822530941</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.7133343101969558</v>
+        <v>-1.111890053971187</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.34285067358023</v>
+        <v>-1.329797752870022</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3606285349556302</v>
+        <v>-0.3474383535960825</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.870079606111695</v>
+        <v>-3.856955656118323</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.956571461451674</v>
+        <v>-3.943419529391058</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.963637980640506</v>
+        <v>-1.3654254115513</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.786813890278083</v>
+        <v>2.799992902382847</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.3490124805436849</v>
+        <v>-0.3356243209808198</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.734629250067016</v>
+        <v>1.748074291382238</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.281920854933851</v>
+        <v>-1.268477244081247</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.350419529953328</v>
+        <v>1.363971391916635</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.600714758147916</v>
+        <v>1.590285122449764</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>175</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.660294203497983</v>
+        <v>-1.647639221171602</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.281058232455393</v>
+        <v>-3.268934254948412</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.449050691786674</v>
+        <v>1.462617106484529</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.9616753245214937</v>
+        <v>-1.255173458852866</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.501688141647264</v>
+        <v>-1.488522342730278</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.8959412207107817</v>
+        <v>-1.190320653826547</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.4100421295350998</v>
+        <v>-0.3970031517400372</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.017327498123755</v>
+        <v>-2.004536365427263</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.344678975414418</v>
+        <v>1.357855679107374</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4961644987121261</v>
+        <v>0.5095514257323899</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.8627962703366947</v>
+        <v>0.8762400206090319</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.04000069479784</v>
+        <v>2.05344409826246</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.76324919621279</v>
+        <v>2.776800817556165</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.442590439718252</v>
+        <v>2.432160804019979</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>208</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.260066352844639</v>
+        <v>-2.247505422565801</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.955601745173446</v>
+        <v>-1.943151395316782</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4326690481982496</v>
+        <v>-0.4196338581718919</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.261278287312955</v>
+        <v>-1.248510085527023</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.817098183225049</v>
+        <v>1.570960049814232</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.552975208648384</v>
+        <v>3.567374523501208</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.9497056094825</v>
+        <v>3.962743931597046</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.003580554828446</v>
+        <v>3.017923642069618</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.943387210426899</v>
+        <v>2.956562165506334</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.016207150225213</v>
+        <v>4.029593349440752</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.254001541830895</v>
+        <v>5.267445041382764</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.368617756134171</v>
+        <v>3.382060411735743</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.508026641561209</v>
+        <v>1.521577636757307</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3162168133446244</v>
+        <v>0.3057871776465859</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>206</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.591960712728124</v>
+        <v>1.604704277962689</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.487347772872106</v>
+        <v>-1.474802626681289</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4316600840505984</v>
+        <v>-0.4186205894799357</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2993120151971311</v>
+        <v>-0.2862456078681319</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.234096462555684</v>
+        <v>-4.222132238459942</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.415983450820605</v>
+        <v>-4.404109673429723</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.333045181771276</v>
+        <v>-1.580463674713116</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.6191455820310097</v>
+        <v>0.6328397314255199</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3373166795588389</v>
+        <v>0.08912381166805261</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2497750068607729</v>
+        <v>-0.5018067665418684</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4542337058267947</v>
+        <v>-0.4407938475254838</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.006201503606505</v>
+        <v>2.01964261653476</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.8391169188856722</v>
+        <v>-0.8255668714999729</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1038728057740101</v>
+        <v>-0.1143024414722689</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>209</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.250785372100687</v>
+        <v>-2.49030946270473</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.727215629114902</v>
+        <v>-6.716649632395736</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-10.94392344788352</v>
+        <v>-10.93473815032291</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-6.991781278838836</v>
+        <v>-6.981158430363763</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-7.529503554202734</v>
+        <v>-7.518923778678143</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-6.27712604322533</v>
+        <v>-6.266113619336146</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-5.88424220107224</v>
+        <v>-5.872993584152582</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.439757179794398</v>
+        <v>-4.427842013373336</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.412175864711564</v>
+        <v>-6.400857168468846</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.872266206281139</v>
+        <v>-4.860163707802926</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-6.034260213744631</v>
+        <v>-6.020825200551556</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.523330206596434</v>
+        <v>-5.509892698391084</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.161861895768091</v>
+        <v>-1.148312800314613</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.347566771491692</v>
+        <v>-2.357996407189738</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>190</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3871601840579899</v>
+        <v>-0.3748916389466714</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.309470401764891</v>
+        <v>4.324022785500837</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.8139661176032149</v>
+        <v>-0.8013849851485375</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-6.46481325061719</v>
+        <v>-6.454353461828845</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.527911937951735</v>
+        <v>-7.51773006648984</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-7.231278820537128</v>
+        <v>-7.220962652080303</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-5.739784751633096</v>
+        <v>-5.728765329609274</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.681019674821997</v>
+        <v>-5.669793669332932</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.216706587076558</v>
+        <v>-5.205212148041639</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-5.014761502283335</v>
+        <v>-5.002920347269026</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-4.695359669286177</v>
+        <v>-4.681927838737899</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-6.239997808928237</v>
+        <v>-6.22656303354605</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.031539751413284</v>
+        <v>-4.017992197343759</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.204026101635129</v>
+        <v>-2.214455737333282</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>223</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>5.793025181944628</v>
+        <v>5.807922627471818</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.840458877018854</v>
+        <v>2.854669145481616</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6565333331337371</v>
+        <v>0.6696746394865798</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.024928643257425</v>
+        <v>3.039044532803992</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1984053811181496</v>
+        <v>-0.1855753671795028</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.09808344135738167</v>
+        <v>0.1110838260253146</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.463683507207257</v>
+        <v>-4.452477689893826</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.2444563441654</v>
+        <v>-2.232092672402807</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.648695551089439</v>
+        <v>-3.636827189437</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.811729377693752</v>
+        <v>-1.798781727038666</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.808358909541589</v>
+        <v>-3.794931440419347</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.534830950412093</v>
+        <v>-1.521397851644977</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.851763590824966</v>
+        <v>-2.838217421635783</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.948184704420122</v>
+        <v>-3.95861434011816</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>185</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.534443025791262</v>
+        <v>1.547793190712021</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.790923636137279</v>
+        <v>-2.779112612870776</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.897455629138598</v>
+        <v>-5.887371352695531</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.064058260364156</v>
+        <v>-3.052588275834829</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.451294423319105</v>
+        <v>-1.439107613303449</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.22795417787048</v>
+        <v>-2.216056042667326</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.394030780111969</v>
+        <v>-3.382678869460484</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-6.021770186271937</v>
+        <v>-6.011340092851476</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.002279092509234</v>
+        <v>-4.991302724027271</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.536829645433869</v>
+        <v>-1.523840485316505</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.9029432497376249</v>
+        <v>-1.189594529717787</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.591673696936752</v>
+        <v>1.30615773725048</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.17268539528007</v>
+        <v>1.186230483537443</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.044907042034858</v>
+        <v>3.034477406336585</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>195</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.23510540327441</v>
+        <v>-2.223544443861378</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7657292278984045</v>
+        <v>0.7791658928356355</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.909286154807305</v>
+        <v>1.922838094063991</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.063535666599513</v>
+        <v>3.077881940065218</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>7.648840187132556</v>
+        <v>7.665557818874817</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>6.408828917234125</v>
+        <v>6.42497447547202</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>7.348918141154293</v>
+        <v>7.36549609962254</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>5.345108096766083</v>
+        <v>5.360883363801726</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.8635166616166785</v>
+        <v>-0.8508343057444137</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.87253343875706</v>
+        <v>1.887206335498362</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.204747109108048</v>
+        <v>3.220219443803394</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>5.800336746779521</v>
+        <v>5.817252118372963</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5.38377590919081</v>
+        <v>5.397320060885036</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>5.636729633857563</v>
+        <v>5.626299998159297</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>191</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.523234488450498</v>
+        <v>3.537891577984396</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.8674057218811058</v>
+        <v>0.8810176986938245</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.520177684702773</v>
+        <v>1.533626858072175</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.148869103918621</v>
+        <v>-5.138939320210511</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-6.209833660893189</v>
+        <v>-6.200280648969446</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.252212529290254</v>
+        <v>-2.24035628940652</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.813808954517491</v>
+        <v>-1.80171789793809</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.280517193184856</v>
+        <v>-2.268548961667769</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.295064310234359</v>
+        <v>-1.282744524200034</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.9923275666942075</v>
+        <v>1.006775838720664</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.781362473644343</v>
+        <v>-0.767733991686228</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.867222268569634</v>
+        <v>1.882645476663548</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.167076156584947</v>
+        <v>-1.15353639015148</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.6535104098004041</v>
+        <v>0.6430807741023727</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>215</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.06383184302686828</v>
+        <v>0.07678881852585562</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.080979070226483</v>
+        <v>-1.068457785147622</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.08029645925043383</v>
+        <v>-0.06777909251171366</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.5143885757924096</v>
+        <v>0.5272201418292681</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.416952411541381</v>
+        <v>-1.405203716001864</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.514234734300722</v>
+        <v>-2.502866235208955</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.6527315485546623</v>
+        <v>0.6661803823329748</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.579670914177058</v>
+        <v>1.593847539352723</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4.306239873722504</v>
+        <v>4.321998642903196</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.189708075836933</v>
+        <v>-1.176412931041305</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.645860652246597</v>
+        <v>-4.634720692091726</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-6.935140747255851</v>
+        <v>-6.924964863588208</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-6.893310734673811</v>
+        <v>-6.879777723582265</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-6.647110556959539</v>
+        <v>-6.657540192657635</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>191</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.183801245292351</v>
+        <v>-1.171647231295367</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.389679671899842</v>
+        <v>1.403934778415355</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.519940260093179</v>
+        <v>1.533508145767257</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6044444478784783</v>
+        <v>0.6172986075204321</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>5.294865992672783</v>
+        <v>5.311231481478309</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.977151282288226</v>
+        <v>2.992126663503271</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.414703822893351</v>
+        <v>3.430339537887804</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.425234166234446</v>
+        <v>2.440347660450364</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.7723263041251585</v>
+        <v>-0.7595954164334486</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.099675052497631</v>
+        <v>-1.086345889723475</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.349098928325823</v>
+        <v>-2.336942533163146</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.792919691880883</v>
+        <v>-1.779886236545877</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.212927692313208</v>
+        <v>-2.19939985744805</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1299502003765056</v>
+        <v>0.1195205646782966</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.336408687940484</v>
+        <v>4.319590211207093</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.122105688602616</v>
+        <v>2.118542102620573</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.06571051142671536</v>
+        <v>-0.04838089166388215</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.1249134525941</v>
+        <v>-1.100573620230428</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.853171758083306</v>
+        <v>-2.821216906406939</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.147409724117502</v>
+        <v>-3.11556492544166</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.635129304649119</v>
+        <v>-2.609451183074597</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.320414692621583</v>
+        <v>-1.302508184184809</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.168265805961433</v>
+        <v>-3.136668175421498</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.639097826797517</v>
+        <v>-1.621815366515769</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.442770371066651</v>
+        <v>-2.417019931038901</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6200119199947807</v>
+        <v>-0.6097205002657162</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.335102030573687</v>
+        <v>1.335798198693105</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.4621714650436459</v>
+        <v>-0.2119643016434694</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>181</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.768228011056344</v>
+        <v>-2.755705721380721</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.481741395208331</v>
+        <v>-5.46883158563228</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-5.874350532965437</v>
+        <v>-5.861343401547835</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.880442588188338</v>
+        <v>-1.867463445789873</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.418603083779061</v>
+        <v>-2.405492279404122</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.121769491520183</v>
+        <v>-2.108726595225818</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.207111554249259</v>
+        <v>-2.194045299948783</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-4.881737661653247</v>
+        <v>-4.868556652358009</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.941868482897291</v>
+        <v>-4.928669743942528</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.032798915264401</v>
+        <v>-3.01939378761157</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.132657647604049</v>
+        <v>-2.119200353893831</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.9956394671202489</v>
+        <v>-0.9821871784001388</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.415654965170496</v>
+        <v>-1.401555873269103</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4915249306416314</v>
+        <v>0.4810952949434792</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>157</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.230001945419708</v>
+        <v>3.242524235095331</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.581788719003896</v>
+        <v>-1.568878909427845</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.739031002197592</v>
+        <v>3.752038133615194</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.324743366597993</v>
+        <v>1.337722508996457</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-5.585042559524403</v>
+        <v>-5.571931755149464</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.461422665451593</v>
+        <v>-1.448379769157228</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.9046918021629011</v>
+        <v>-0.8916255478624251</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.808316269450081</v>
+        <v>1.821497278745319</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.377799193567377</v>
+        <v>2.39099793252214</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.287522177556333</v>
+        <v>-2.274117049903502</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.6859780090626018</v>
+        <v>0.6994353027728195</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.09095910077199</v>
+        <v>-3.07750681205188</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-5.071917061802765</v>
+        <v>-5.414299569216588</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-8.00690910532262</v>
+        <v>-8.017338741020772</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>107</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.156989722079139</v>
+        <v>-0.1444674324035162</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.969754421965952</v>
+        <v>1.982664231542003</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.444044593874146</v>
+        <v>3.457051725291748</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.639718287229307</v>
+        <v>2.652697429627771</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.2321381936523537</v>
+        <v>0.2452489980272929</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5295801313680712</v>
+        <v>0.5426230276624366</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.4448464140957356</v>
+        <v>0.4579126683962116</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.781401333071244</v>
+        <v>2.794582342366482</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.589560325393613</v>
+        <v>4.602759064348376</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.870276261861015</v>
+        <v>1.883681389513846</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.665522937543436</v>
+        <v>1.678980231253654</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.569064973393537</v>
+        <v>3.582517262113647</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.083389801700932</v>
+        <v>4.096945848052535</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.463952255472648</v>
+        <v>2.453522619774496</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>143</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-6.339592166363779</v>
+        <v>-6.327069876688157</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.538344710182415</v>
+        <v>2.551254519758466</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.241378101487882</v>
+        <v>4.254385232905484</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.770232632696782</v>
+        <v>5.783211775095246</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>8.029014214827448</v>
+        <v>8.042125019202388</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>9.025756851843802</v>
+        <v>9.038799748138167</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.24172243527083</v>
+        <v>8.254788689571306</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.977336239286522</v>
+        <v>4.99051724858176</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.419832856600735</v>
+        <v>1.433031595555498</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.5697076715728073</v>
+        <v>0.5831127992256384</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.064255046555878</v>
+        <v>1.077712340266096</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.698564593301477</v>
+        <v>-1.685112304581367</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.02091710634428523</v>
+        <v>-0.007361059992682328</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.267699270571491</v>
+        <v>-3.278128906269643</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>120</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.006561679789982122</v>
+        <v>0.01908396946560487</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.894988066825746</v>
+        <v>5.907897876401798</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.50011936022918</v>
+        <v>10.51312649164678</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.29703915950337</v>
+        <v>7.310018301901835</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.091951277764529</v>
+        <v>5.105062082139469</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.804659498207883</v>
+        <v>2.817725752508359</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.504142766093054</v>
+        <v>1.517323775388292</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.44314287991071</v>
+        <v>1.456341618865473</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.740315638450483</v>
+        <v>-2.726910510797651</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.4450689627680404</v>
+        <v>-0.4316116690578227</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.244019138755959</v>
+        <v>-1.230566850035849</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.8309404163675111</v>
+        <v>-0.8173843700159082</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.085447582575391</v>
+        <v>1.075017946877239</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>76</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-7.756596214946818</v>
+        <v>-7.744073925271195</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-5.420801406858409</v>
+        <v>-5.407891597282358</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.394856202334445</v>
+        <v>3.407863333752047</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.73804855979494</v>
+        <v>-1.725069417396476</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.618267067238158</v>
+        <v>5.631377871613097</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.284130057585436</v>
+        <v>3.297172953879802</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.5678173929447397</v>
+        <v>0.5808836472452157</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.53094495320515</v>
+        <v>-2.517763943909912</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.907734313071664</v>
+        <v>-3.894535574116901</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.5052983966371798</v>
+        <v>0.5187035242900109</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.616334546003849</v>
+        <v>1.629791839714066</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.612440191387527</v>
+        <v>-3.598987902667417</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.230463092404378</v>
+        <v>1.244019138755981</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.795973898364863</v>
+        <v>2.785544262666711</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>83</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.72342914966957</v>
+        <v>1.735951439345193</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.726313368030581</v>
+        <v>3.739223177606632</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-5.102290278325043</v>
+        <v>-5.089283146907441</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-7.381675699934405</v>
+        <v>-7.368696557535941</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-6.715277637898112</v>
+        <v>-6.702166833523172</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-8.827474254399313</v>
+        <v>-8.814431358104947</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-8.912207971671627</v>
+        <v>-8.899141717371151</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-3.355294984910991</v>
+        <v>-3.342113975615753</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-4.621114148201734</v>
+        <v>-4.607915409246971</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-5.47123933322959</v>
+        <v>-5.457834205576759</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-10.49526976598094</v>
+        <v>-10.48181247227072</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-10.46088660863547</v>
+        <v>-10.44743431991536</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-4.857044834038206</v>
+        <v>-4.843488787686603</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-8.22178133308725</v>
+        <v>-8.232210968785402</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>70</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.220847394075719</v>
+        <v>3.233369683751341</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.466416638254344</v>
+        <v>4.479326447830395</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.071547931657754</v>
+        <v>4.084555063075356</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.058943921408108</v>
+        <v>7.071923063806572</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.663379849193035</v>
+        <v>3.676490653567974</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.960821786908696</v>
+        <v>3.973864683203061</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.838197644649249</v>
+        <v>-1.825131390348773</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.305381043430749</v>
+        <v>-2.292200034135512</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.347904784672615</v>
+        <v>3.361103523627378</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.78793468606959</v>
+        <v>-1.774529558416759</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.86445484675572</v>
+        <v>0.8779121404659378</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.8988380041010728</v>
+        <v>0.9122902928211829</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.4785833931562138</v>
+        <v>0.4921394395078167</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>55</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.40252922930091</v>
+        <v>-3.390006939625287</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-14.10501193317423</v>
+        <v>-14.09210212359818</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-7.227153367043549</v>
+        <v>-7.214146235625947</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1758270382912528</v>
+        <v>0.188806180689717</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.910133095946321</v>
+        <v>6.92324390032126</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-5.519697693610738</v>
+        <v>-5.506654797316372</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-9.240795047246657</v>
+        <v>-9.227728792946181</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-11.52616026420998</v>
+        <v>-11.51297925491474</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6.132614695846769</v>
+        <v>-6.119415956892006</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.982739880874746</v>
+        <v>-6.969334753221915</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-9.005675023374145</v>
+        <v>-8.992217729663928</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1196172248804288</v>
+        <v>0.1330695136005389</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.3006373860645297</v>
+        <v>-0.2870813397129268</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.869097871970062</v>
+        <v>-1.879527507668215</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>39</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9.045023218251565</v>
+        <v>9.057545507927188</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2588580870203856</v>
+        <v>-0.2459482774443345</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.910375770485622</v>
+        <v>1.923382901903224</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.604731467195656</v>
+        <v>4.61771060959412</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>14.32272050853378</v>
+        <v>14.33583131290872</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.927854753941745</v>
+        <v>6.94089765023611</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.84312103666943</v>
+        <v>6.856187290969906</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>11.51732377538828</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>14.00724544401336</v>
+        <v>14.02044418296812</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13.15712025898543</v>
+        <v>13.17052538663826</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>18.08057206287297</v>
+        <v>18.09402935658319</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>15.55085265611581</v>
+        <v>15.56430494483592</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15.13059804517093</v>
+        <v>15.14415409152254</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>15.38031937744719</v>
+        <v>15.36988974174904</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>51</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.513046163347234</v>
+        <v>-1.500523873671611</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-5.085404090036981</v>
+        <v>-5.07249428046093</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-7.441057110359083</v>
+        <v>-7.42804997894148</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-7.310803977751597</v>
+        <v>-7.297824835353133</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.966872251647288</v>
+        <v>-1.953761447272349</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-9.512567568833582</v>
+        <v>-9.499524672539216</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.754164031203871</v>
+        <v>-1.741097776903395</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.6610055111911</v>
+        <v>3.674186520486337</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.482358566185233</v>
+        <v>9.495557305139997</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.55380200860827</v>
+        <v>12.5672071362611</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>12.34904868429071</v>
+        <v>12.36250597800093</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>12.38343184163617</v>
+        <v>12.39688413035628</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>13.92396154441672</v>
+        <v>13.93751759076832</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.21289856296757</v>
+        <v>12.20246892726941</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that VOL Ratio-7-21 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that VOL Ratio-7-21 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4073</v>
+        <v>4074</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.07053083122319492</v>
+        <v>-0.07083528671248018</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.004644736111806935</v>
+        <v>-0.004975349246734595</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.01897956239569965</v>
+        <v>-0.01930924886729457</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.02233385053829551</v>
+        <v>-0.02266207681187637</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.0574852729459252</v>
+        <v>-0.05780835626368486</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03286295328952349</v>
+        <v>0.03251940427820443</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.05956145899220644</v>
+        <v>0.0592106826725427</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.02257048530528749</v>
+        <v>0.02222573617260792</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.000375184499901593</v>
+        <v>-0.0007148492230655279</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.05206447337815234</v>
+        <v>-0.05239686031540458</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.09587040208767661</v>
+        <v>-0.09619346940125695</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1213197522529157</v>
+        <v>-0.121636526188972</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1596100285423248</v>
+        <v>-0.1599201573370124</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1415349855562056</v>
+        <v>-0.1412314394752343</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4016</v>
+        <v>4017</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.0734829963082646</v>
+        <v>-0.07396813971549676</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2072959450908129</v>
+        <v>-0.2077635780533882</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1417976996168591</v>
+        <v>-0.1422856235468686</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2215897525681854</v>
+        <v>-0.2220568574392985</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2745083495646838</v>
+        <v>-0.2749677241198683</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2119984346192325</v>
+        <v>-0.2124707205236049</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2583531788987514</v>
+        <v>-0.2588150029588334</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2893264863518326</v>
+        <v>-0.2897853471570642</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2620714117248255</v>
+        <v>-0.2625378772392395</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.252753449395783</v>
+        <v>-0.2532306633302142</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.3192084667906485</v>
+        <v>-0.3196713705504024</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.3704501989849547</v>
+        <v>-0.3709002663085812</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.403382537353373</v>
+        <v>-0.4038287038470472</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.4135564014883499</v>
+        <v>-0.4130328372900394</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3948</v>
+        <v>3949</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.05718484886435959</v>
+        <v>-0.05789735309870991</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.3423856705479622</v>
+        <v>-0.343048854221756</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2690142593717297</v>
+        <v>-0.2697017911815038</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3524471130248727</v>
+        <v>-0.3531121182379664</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3717838751290969</v>
+        <v>-0.372451813767583</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.3638929321436919</v>
+        <v>-0.3645590866080752</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.5613329164570899</v>
+        <v>-0.5619506883409713</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.5595901625867654</v>
+        <v>-0.5602152048055586</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.5308852843526779</v>
+        <v>-0.5315187756716639</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.5068473523506327</v>
+        <v>-0.5074990933088515</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.5456764039222293</v>
+        <v>-0.5463215206098226</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.6997153412876358</v>
+        <v>-0.7003213425694099</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.6500929444337373</v>
+        <v>-0.6507177033492795</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.6394764295826505</v>
+        <v>-0.6387070467920353</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3860</v>
+        <v>3861</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1530889196557581</v>
+        <v>0.1520215017320368</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2568714373064651</v>
+        <v>-0.2578650980365964</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2761658373941813</v>
+        <v>-0.2771627645515693</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.4419789283519506</v>
+        <v>-0.442930979076408</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.5012252536389568</v>
+        <v>-0.5021730599794125</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.4482489768672906</v>
+        <v>-0.4492051391947101</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.6224157539255444</v>
+        <v>-0.6233290561782852</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.5324152611530195</v>
+        <v>-0.533361510362937</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.4757876936123182</v>
+        <v>-0.476750293533172</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5094667771668639</v>
+        <v>-0.5104378932901312</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5186300983276695</v>
+        <v>-0.5196033874843735</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.6769554411899534</v>
+        <v>-0.6778875852157853</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4612175466446899</v>
+        <v>-0.4622143372177518</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.4819099303779666</v>
+        <v>-0.4809261090668073</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3757</v>
+        <v>3758</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.07950597687224814</v>
+        <v>0.0780868864637938</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4568293913859591</v>
+        <v>-0.4581498689562693</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3332139731041579</v>
+        <v>-0.3345784698814782</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4805911387003476</v>
+        <v>-0.4819137575461667</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.6064024131542425</v>
+        <v>-0.6077066993843161</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.6663836769501117</v>
+        <v>-0.6676647910401243</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.7102182913776645</v>
+        <v>-0.7114907149551044</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.6581391012113968</v>
+        <v>-0.659438534211418</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6780692413013725</v>
+        <v>-0.6793657068497794</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7426199901300237</v>
+        <v>-0.7439227383362237</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.7464874024843979</v>
+        <v>-0.7477953081609385</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.7505368296312227</v>
+        <v>-0.7518434457805654</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.6504366022820491</v>
+        <v>-0.6517818161452382</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.6519758936024118</v>
+        <v>-0.6506339956453715</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3653</v>
+        <v>3654</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.04338655704043504</v>
+        <v>0.04158192419703255</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6807281678263379</v>
+        <v>-0.6823912670788133</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.4332867533079465</v>
+        <v>-0.43503176210492</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.6431737807095956</v>
+        <v>-0.6448579717517546</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.7300039379645966</v>
+        <v>-0.7316837546063937</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.8274874182264682</v>
+        <v>-0.8291313377066274</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.7609142722839195</v>
+        <v>-0.762580174833893</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.7214197737630101</v>
+        <v>-0.7231133830816532</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.6855248802496234</v>
+        <v>-0.6872313063417295</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.8371162947261439</v>
+        <v>-0.8388113673677537</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.8899996702808508</v>
+        <v>-0.8916882345487096</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.8131025860884122</v>
+        <v>-0.8148119266223119</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.6708418942000733</v>
+        <v>-0.6726055282466845</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.570041056899008</v>
+        <v>-0.5683865413548261</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3522</v>
+        <v>3523</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.05855723300724947</v>
+        <v>-0.06087640415450579</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.6508782978401442</v>
+        <v>-0.637968488264093</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.4228704472453444</v>
+        <v>-0.4098633158277423</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6171494556198525</v>
+        <v>-0.6193890216164988</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.7437427732269981</v>
+        <v>-0.7459716193615407</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.7143188842648058</v>
+        <v>-0.7165440581971367</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.6420525199326974</v>
+        <v>-0.6443031508636992</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.7124105218888062</v>
+        <v>-0.6992295125935684</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.8146777419586329</v>
+        <v>-0.8169010115199669</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.855271206610837</v>
+        <v>-0.8575219841933901</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.9876221542574442</v>
+        <v>-0.9898457397706721</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.7956649957366935</v>
+        <v>-0.7979427365606924</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.7460222594936852</v>
+        <v>-0.7483340484117136</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.6507818325296597</v>
+        <v>-0.6486550590835805</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.02519059186155204</v>
+        <v>0.02206370724871931</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.5133576857822817</v>
+        <v>-0.5004478762062305</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.5207450212909421</v>
+        <v>-0.50773788987334</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.5991357038846346</v>
+        <v>-0.5861565614861703</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.7041131229510569</v>
+        <v>-0.7071584841794802</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.7048226461775471</v>
+        <v>-0.6917797498831817</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.6541833291109356</v>
+        <v>-0.6572295247724966</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.6441821170961219</v>
+        <v>-0.6310011078008841</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.9275810659921859</v>
+        <v>-0.9305755697218174</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.9259318724105228</v>
+        <v>-0.9289789276632234</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.084372445355143</v>
+        <v>-1.087386064760643</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.9439295597771959</v>
+        <v>-0.9469847604836374</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.9295067246112865</v>
+        <v>-0.9325928899721632</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.8125207472722309</v>
+        <v>-0.8096893410558437</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3139</v>
+        <v>3140</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1766188953017789</v>
+        <v>0.1724045922810262</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4177900641341878</v>
+        <v>-0.4048802545581367</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.5265812119259436</v>
+        <v>-0.5135740805083415</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.555260056432239</v>
+        <v>-0.5422809140337748</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.8711765035450867</v>
+        <v>-0.8580656991701474</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.986957706325299</v>
+        <v>-0.9739148100309336</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.9592514715854321</v>
+        <v>-0.9632659830288262</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.8858943298263924</v>
+        <v>-0.8727133205311546</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.184083583193576</v>
+        <v>-1.188067496131829</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.253413527940381</v>
+        <v>-1.257444861942716</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.504373015388495</v>
+        <v>-1.50834302975359</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.229692491191514</v>
+        <v>-1.233749536223016</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.09102534205757</v>
+        <v>-1.095162147793729</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.8873144435475737</v>
+        <v>-0.8835807792374055</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.07721200324933619</v>
+        <v>0.07184094700139099</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.3426694067867615</v>
+        <v>-0.3297595972107104</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.5332480214528132</v>
+        <v>-0.5202408900352111</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5732366321207536</v>
+        <v>-0.5602574897222894</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6349809660216721</v>
+        <v>-0.6218701616467328</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.7461192121670948</v>
+        <v>-0.7330763158727294</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.9329979754046391</v>
+        <v>-0.9199317211041631</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9916011903250634</v>
+        <v>-0.9784201810298256</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.290939517092994</v>
+        <v>-1.277740778138231</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.323904334398748</v>
+        <v>-1.310499206745916</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.578129816537391</v>
+        <v>-1.583297062316291</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.456966327853095</v>
+        <v>-1.46217447946367</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.108718194145332</v>
+        <v>-1.114090786824583</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.9423396659755809</v>
+        <v>-0.9375928234022339</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2724</v>
+        <v>2725</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2558285419601134</v>
+        <v>0.2683508316357361</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1471874803155018</v>
+        <v>0.1600972898915529</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2655152546573234</v>
+        <v>0.2785223860749255</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.08077120217799205</v>
+        <v>-0.06779205977952785</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.1059959363117429</v>
+        <v>-0.09288513193680359</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3217504795345008</v>
+        <v>-0.3087075832401354</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5531117627891788</v>
+        <v>-0.5400455084887028</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7270400296058739</v>
+        <v>-0.7138590203106361</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.8980105902749784</v>
+        <v>-0.8848118513202152</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.051654836886485</v>
+        <v>-1.038249709233654</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.236231412346385</v>
+        <v>-1.242950867493846</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.144972917185918</v>
+        <v>-1.151725632580799</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.104640722177955</v>
+        <v>-1.111466052578926</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.834523048848979</v>
+        <v>-0.8286517778933984</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3040400091832467</v>
+        <v>0.3165622988588694</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1649016100851881</v>
+        <v>-0.151991800509137</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3464550576287095</v>
+        <v>0.3594621890463117</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3979059837744288</v>
+        <v>0.410885126172893</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.4505013171656103</v>
+        <v>0.4636121215405495</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1963278096487997</v>
+        <v>0.2093707059431651</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.1642136302397077</v>
+        <v>-0.1511473759392317</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.3555893064049798</v>
+        <v>-0.342408297109742</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5741936055108425</v>
+        <v>-0.5609948665560793</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.7545000356136242</v>
+        <v>-0.7410949079607931</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.9768650473824607</v>
+        <v>-0.9851971694518795</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.7629465835509421</v>
+        <v>-0.7713630660390294</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.8851810475312618</v>
+        <v>-0.893619911551184</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.7318373424443294</v>
+        <v>-0.7247848144639804</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.225619745695937</v>
+        <v>-0.2130974560203143</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.4549039418135337</v>
+        <v>-0.4419941322374825</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3165340470542333</v>
+        <v>0.3295411784718354</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.1444113697265266</v>
+        <v>0.1573905121249908</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.5131175844599767</v>
+        <v>0.526228388834916</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.2058079023052244</v>
+        <v>0.2188507985995898</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.2506638178623177</v>
+        <v>0.2637300721627938</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.1733230366427208</v>
+        <v>-0.160142027347483</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2775194671014845</v>
+        <v>-0.2643207281467213</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.652482665088371</v>
+        <v>-0.63907753743554</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7036399797660735</v>
+        <v>-0.7141890628663603</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6884635832004307</v>
+        <v>-0.6990197454550611</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.6954156182130049</v>
+        <v>-0.7060570894279721</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4214758272039205</v>
+        <v>-0.4128713264791628</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3787766660746357</v>
+        <v>-0.3662543763990129</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.2516284745276138</v>
+        <v>-0.2387186649515627</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.857262217372039</v>
+        <v>0.8702693487896411</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.4236055755434478</v>
+        <v>0.436584717941912</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.6840565409224055</v>
+        <v>0.6971673452973448</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.4175887042019752</v>
+        <v>0.4306316004963406</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5678173929447397</v>
+        <v>0.5808836472452157</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.335596400178261</v>
+        <v>0.3487774094734988</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1336190703869491</v>
+        <v>0.1468178093417123</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.575528671031968</v>
+        <v>-0.5621235433791369</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.6862970329435214</v>
+        <v>-0.6728397392333036</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.8868762816131266</v>
+        <v>-0.8734239928930165</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.8579737967154628</v>
+        <v>-0.8706425153793589</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.7231130947529181</v>
+        <v>-0.7127112491735303</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1913172648556056</v>
+        <v>-0.1787949751799829</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.354365269956439</v>
+        <v>-0.3414554603803879</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7510246887340983</v>
+        <v>0.7640318201517005</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.1570150174098757</v>
+        <v>0.1699941598083399</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.01927479569643253</v>
+        <v>-0.006163991321493256</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1874303747940189</v>
+        <v>-0.1743874784996535</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.1169649197952154</v>
+        <v>-0.1038986654947394</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.1702838591871654</v>
+        <v>-0.1571028498919276</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2343137714437731</v>
+        <v>0.2475125103985363</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.822743643278919</v>
+        <v>-0.8093385156260879</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.079230025020195</v>
+        <v>-1.065772731309977</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.562177441911707</v>
+        <v>-1.548725153191597</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.488290312847887</v>
+        <v>-1.503278489691766</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.365355110329837</v>
+        <v>-1.352518285006809</v>
       </c>
     </row>
     <row r="21">
@@ -2994,49 +2994,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.5990640377759888</v>
+        <v>-0.5865417481003661</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4884792121638952</v>
+        <v>-0.4755694025878441</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.6665946759582226</v>
+        <v>0.6796018073758248</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.7394425272798415</v>
+        <v>0.7524216696783057</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6602635624946984</v>
+        <v>0.6733743668696377</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.03922099963631354</v>
+        <v>0.05226389593067893</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.0692978449357895</v>
+        <v>0.08236409923626553</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.06135669644131525</v>
+        <v>0.07453770573655305</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.4021937792601662</v>
+        <v>0.4153925182149294</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.02198421862655</v>
+        <v>-1.008579090973718</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.111926980372374</v>
+        <v>-1.098469686662156</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.938623042315115</v>
+        <v>-1.925170753595005</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.523550027702036</v>
+        <v>-1.541647668906123</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.586966210528054</v>
+        <v>-1.571449600509311</v>
       </c>
     </row>
     <row r="22">
@@ -3046,49 +3046,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6925214898235978</v>
+        <v>-0.6799992001479751</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4049464452894895</v>
+        <v>-0.3920366357134384</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.7718940819056712</v>
+        <v>0.7849012133232733</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.7711714450305251</v>
+        <v>0.7841505874289894</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.953116962112901</v>
+        <v>0.9662277664878403</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.3992163981913706</v>
+        <v>0.4122592944857359</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.01295674278753012</v>
+        <v>0.0001095115129459145</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1527007178624089</v>
+        <v>-0.1395197085671711</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1482127193033875</v>
+        <v>-0.1350139803486243</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.998337904331315</v>
+        <v>-0.9849327766784839</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.6137002659769948</v>
+        <v>-0.600242972266777</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.234195956044786</v>
+        <v>-1.220743667324676</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.7665017968830696</v>
+        <v>-0.7895520190008938</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.8735688108672193</v>
+        <v>-0.854864097683695</v>
       </c>
     </row>
     <row r="23">
@@ -3098,49 +3098,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.622180835180032</v>
+        <v>-0.6096585455044092</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.6618981607191472</v>
+        <v>-0.6489883511430961</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.6647900189118161</v>
+        <v>0.6777971503294182</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.7950431515193159</v>
+        <v>0.8080222939177801</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.331472235848338</v>
+        <v>0.3445830402232772</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.03011177835441714</v>
+        <v>0.04315467464878253</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.5037237353250461</v>
+        <v>-0.4906574810245701</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5218053376993623</v>
+        <v>-0.5086243284041245</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.05885312807327381</v>
+        <v>-0.04565438911851061</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.9838286125023998</v>
+        <v>-0.9704234848495688</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.3652286434068017</v>
+        <v>-0.351771349696584</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.154198779474548</v>
+        <v>-1.140746490754438</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5594048358432175</v>
+        <v>-0.5878434518522795</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.01725106809927</v>
+        <v>-0.9942704426358588</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1166</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.33662598087836</v>
+        <v>-1.324103691202737</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.063023929746642</v>
+        <v>-1.050114120170591</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.7700422394065569</v>
+        <v>0.783049370824159</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.071674977840964</v>
+        <v>1.084654120239428</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.7903231715091579</v>
+        <v>0.8034339758840972</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4879364888306412</v>
+        <v>0.5009793851250066</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.196625848835815</v>
+        <v>-0.183559594535339</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.4067398388769519</v>
+        <v>-0.3935588295817141</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.3891583040752735</v>
+        <v>0.4023570430300367</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.8894158955199174</v>
+        <v>-0.8760107678670863</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.06589158487605573</v>
+        <v>-0.05243429116583798</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.231165668318972</v>
+        <v>-1.217713379598862</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8323698045893977</v>
+        <v>-0.8666560066911941</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.097228232175887</v>
+        <v>-1.107657867874039</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>985</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.073560024063923</v>
+        <v>-1.0610377343883</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.251056557920684</v>
+        <v>-0.2381467483446329</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.990991571182526</v>
+        <v>2.003998702600128</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.614145312309297</v>
+        <v>1.627124454707761</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.379983732125567</v>
+        <v>1.393094536500506</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.9674865217682012</v>
+        <v>0.9805294180625665</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.1728136564229033</v>
+        <v>0.1858799107233793</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4155694057144217</v>
+        <v>0.4287504150096595</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.368768302493585</v>
+        <v>1.381967041448348</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.4955556654958073</v>
+        <v>-0.4821505378429762</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.3138897931480784</v>
+        <v>0.3273470868582962</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.274445102244826</v>
+        <v>-1.260992813524716</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.7251874552846473</v>
+        <v>-0.7683647621728156</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.389171706764699</v>
+        <v>-1.399601342462852</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>828</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.889573585910455</v>
+        <v>-1.877051296234832</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.001268260062481374</v>
+        <v>0.01417806963853252</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.659539650084255</v>
+        <v>1.672546781501858</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.669019835831854</v>
+        <v>1.681998978230318</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.700646929938422</v>
+        <v>2.713757734313361</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.428040558475345</v>
+        <v>1.441083454769711</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.3771232663238351</v>
+        <v>0.3901895206243111</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.151485761262137</v>
+        <v>0.1646667705573748</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.177442396818961</v>
+        <v>1.190641135773724</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.1557745756485716</v>
+        <v>-0.1423694479957405</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2433368343333626</v>
+        <v>0.2567941280435804</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.9300094769202403</v>
+        <v>-0.9165571882001302</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.0990112744536944</v>
+        <v>0.1125673208052973</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.1343591807096303</v>
+        <v>-0.1447888164077824</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>721</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.146697682207204</v>
+        <v>-2.134175392531581</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2908649151437217</v>
+        <v>-0.2779551055676706</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.394710206276329</v>
+        <v>1.407717337693931</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.524963338883829</v>
+        <v>1.537942481282293</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.066985951828308</v>
+        <v>3.080096756203247</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.561376571929543</v>
+        <v>1.574419468223908</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.367072813048388</v>
+        <v>0.380139067348864</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.2388068409342239</v>
+        <v>-0.2256258316389861</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.6710670592912393</v>
+        <v>0.6842657982460025</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4564506361389036</v>
+        <v>-0.4430455084860725</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.03227731554906654</v>
+        <v>0.0457346092592843</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.597694589518817</v>
+        <v>-1.584242300798707</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4922903932515155</v>
+        <v>-0.4787343468999126</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.5199615713774506</v>
+        <v>-0.5303912070756027</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>578</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.10935527522728</v>
+        <v>-1.096832985551657</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.990825081963159</v>
+        <v>-0.9779152723871078</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.6904307789142976</v>
+        <v>0.7034379103318997</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4746631502761218</v>
+        <v>0.487642292674586</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.839356122055172</v>
+        <v>1.852466926430111</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2853472689488967</v>
+        <v>-0.2723043726545313</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.581153650581037</v>
+        <v>-1.568087396280561</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.529305907494027</v>
+        <v>-1.51612489819879</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.4858187737977175</v>
+        <v>0.4990175127524807</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.7103271724758784</v>
+        <v>-0.6969220448230473</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.2230389743021064</v>
+        <v>-0.2095816805918886</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.572738861939371</v>
+        <v>-1.559286573219261</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.6089104279015771</v>
+        <v>-0.5953543815499742</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.1598420462432202</v>
+        <v>0.149412410545068</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>458</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.401735263441417</v>
+        <v>-1.389212973765794</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.794968265051956</v>
+        <v>-2.782058455475905</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.879793303526284</v>
+        <v>-1.866786172108682</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.312858948211364</v>
+        <v>-1.2998798058129</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.9871477843147218</v>
+        <v>1.000258588689661</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.335497614214155</v>
+        <v>-1.32245471791979</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.730274999608703</v>
+        <v>-2.717208745308227</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.324095952975355</v>
+        <v>-2.310914943680118</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.2349914970868809</v>
+        <v>0.2481902360416441</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.1784524652336259</v>
+        <v>-0.1650473375807948</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1648651781974877</v>
+        <v>-0.1514078844872699</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.658866300328036</v>
+        <v>-1.645414011607926</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.5507366317969584</v>
+        <v>-0.5371805854453555</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.08267468816696066</v>
+        <v>-0.0931043238651128</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>382</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1374173778015972</v>
+        <v>-0.1248950881259745</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.272551200189938</v>
+        <v>-2.259641390613886</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-2.929200011498573</v>
+        <v>-2.91619288008097</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.228266250618816</v>
+        <v>-1.215287108220352</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.06577326729330224</v>
+        <v>0.07888407166824152</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.254585842111453</v>
+        <v>-2.241542945817088</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-3.386439978231898</v>
+        <v>-3.373373723931422</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.282942748741156</v>
+        <v>-2.269761739445919</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.059198726333086</v>
+        <v>1.07239746528785</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3144866681189171</v>
+        <v>-0.301081540466086</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5192399924364963</v>
+        <v>-0.5057826987262786</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.270197149227194</v>
+        <v>-1.256744860507084</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.905111446035967</v>
+        <v>-0.8915553996843641</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6553901137596796</v>
+        <v>-0.6658197494578317</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>299</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.6539734372668349</v>
+        <v>-0.6414511475912121</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-3.937787852906673</v>
+        <v>-3.924878043330622</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.325967596292564</v>
+        <v>-2.312960464874962</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.4798708205958704</v>
+        <v>0.4928499629943346</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.9481385687344</v>
+        <v>1.961249373109339</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4300047778308738</v>
+        <v>-0.4169618815365084</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.852531137243616</v>
+        <v>-1.83946488294314</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.985266375489999</v>
+        <v>-1.972085366194761</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.636007985819333</v>
+        <v>2.649206724774096</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.11698647972117</v>
+        <v>1.130391607374001</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.250025797544069</v>
+        <v>2.263483091254287</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.28106447328414</v>
+        <v>1.29451676200425</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1919135412690025</v>
+        <v>0.2054695876206054</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.444979355150643</v>
+        <v>1.434549719452491</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>229</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.838416486148844</v>
+        <v>-1.825894196473222</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-6.50675865806506</v>
+        <v>-6.493848848489009</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.281540028417112</v>
+        <v>-4.26853289699951</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.531199559565067</v>
+        <v>-1.518220417166603</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.42382900702215</v>
+        <v>1.436939811397089</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.772178836921576</v>
+        <v>-1.75913594062721</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.856912554193855</v>
+        <v>-1.843846299893379</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.887414730267935</v>
+        <v>-1.874233720972697</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.418397610624005</v>
+        <v>2.431596349578768</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.004953648303498</v>
+        <v>2.01835877595633</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.673562769400768</v>
+        <v>2.687020063110985</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.39790225862393</v>
+        <v>1.41135454734404</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1042852022641725</v>
+        <v>0.1178412486157754</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.664050202662736</v>
+        <v>1.653620566964584</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>174</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.344013032853653</v>
+        <v>-1.33149074317803</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-3.3504553524145</v>
+        <v>-3.337448220996897</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.070776932450684</v>
+        <v>-2.05779779005222</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.3103475728102012</v>
+        <v>-0.2972367684352619</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.5876182787727018</v>
+        <v>-0.5745753824783364</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.4770732913113349</v>
+        <v>0.4901395456118109</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.159315179886157</v>
+        <v>1.172496189181395</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.121303799450985</v>
+        <v>5.134502538405748</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.845891258101219</v>
+        <v>4.85929638575405</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.365275864818116</v>
+        <v>6.378733158528334</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.801957872738264</v>
+        <v>1.815410161458374</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2322779744370465</v>
+        <v>0.2458340207886494</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>2.780849881425972</v>
+        <v>2.77042024572782</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>135</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-4.34529017206183</v>
+        <v>-4.332767882386207</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-5.216123044285347</v>
+        <v>-5.203213234709295</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.870251010141196</v>
+        <v>-4.857243878723594</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-3.999257136792956</v>
+        <v>-3.986277994394491</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.537678351865125</v>
+        <v>-4.524567547490186</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-2.758754932667983</v>
+        <v>-2.745712036373618</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.362007168458774</v>
+        <v>-1.348940914158298</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.829190567240275</v>
+        <v>-1.816009557945037</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.554253991021859</v>
+        <v>2.567452729976623</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.444869546734672</v>
+        <v>2.458274674387503</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.980856963157834</v>
+        <v>2.994314256868051</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-2.169945064681912</v>
+        <v>-2.156492775961802</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-4.071681157108301</v>
+        <v>-4.058125110756698</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.8589968618690449</v>
+        <v>-0.869426497567197</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.052344601962922</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-5.295488123650422</v>
+        <v>-5.282578314074371</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-3.309404449294632</v>
+        <v>-3.29639731787703</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-1.988675126210936</v>
+        <v>-1.975695983812471</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-6.098524912711682</v>
+        <v>-6.085414108336742</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.341774167861125</v>
+        <v>1.35481706415549</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.123911930363541</v>
+        <v>-1.110845676063065</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-1.652095215327343</v>
+        <v>-1.63889647637258</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-3.692696590831453</v>
+        <v>-3.679291463178622</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-2.706973724672849</v>
+        <v>-2.693516430962632</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-11.00592390066075</v>
+        <v>-10.99247161194064</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-14.99760708303422</v>
+        <v>-14.98405103668262</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-8.795504798376989</v>
+        <v>-8.805934434075141</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that VOL Ratio-7-21 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that VOL Ratio-7-21 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.458942632170981</v>
+        <v>3.471464921846604</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2620241221339441</v>
+        <v>0.2750312535515462</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.582753445217634</v>
+        <v>1.595732587616098</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.425284611097844</v>
+        <v>3.438395415472783</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1512979773849352</v>
+        <v>0.1643408736793006</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.06656426011265637</v>
+        <v>0.0796305144131324</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.7898570518073456</v>
+        <v>0.8030380611025834</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.300285737053613</v>
+        <v>4.313484476008377</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.021589123454255</v>
+        <v>7.034994251107086</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.007311989612873</v>
+        <v>8.020769283323091</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.232171337434494</v>
+        <v>9.245623626154604</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.19286910744197</v>
+        <v>11.20642515379357</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>141</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.116490757804208</v>
+        <v>2.12901304747983</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.597115726400233</v>
+        <v>7.610025535976284</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.656147729023502</v>
+        <v>3.669154860441104</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.623280294255117</v>
+        <v>6.636259436653582</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.212518653651038</v>
+        <v>8.225629458025978</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.091520875054634</v>
+        <v>7.104563771349</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.134446732250446</v>
+        <v>9.147512986550922</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.376483191624978</v>
+        <v>9.389664200920215</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.02470316359871</v>
+        <v>10.03790190255347</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.883797836726799</v>
+        <v>9.89720296437963</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.09748422872127</v>
+        <v>11.11094152243149</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>12.55030710237877</v>
+        <v>12.56375939109888</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>13.54849220774592</v>
+        <v>13.56204825409752</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>13.7982135400222</v>
+        <v>13.78778390432405</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>209</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.095078426201511</v>
+        <v>1.107600715877133</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.617476105103279</v>
+        <v>7.63038591467933</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.830262900899029</v>
+        <v>4.843270032316632</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.874391631592658</v>
+        <v>6.887370773991123</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.292908215563557</v>
+        <v>7.306019019938496</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.590350153279218</v>
+        <v>7.603393049573583</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.81183653170071</v>
+        <v>11.82490278600119</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>11.34465313291921</v>
+        <v>11.35783414221445</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>11.76212214625844</v>
+        <v>11.7753208852132</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>11.39046586075204</v>
+        <v>11.40387098840488</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>11.664181435956</v>
+        <v>11.67763872966621</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>14.56937799043062</v>
+        <v>14.58283027915073</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>13.67065447996418</v>
+        <v>13.68421052631578</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>13.44190691271893</v>
+        <v>13.43147727702078</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>297</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.98838781515947</v>
+        <v>-1.975865525483847</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.144146315984017</v>
+        <v>4.157056125560068</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.412577272687095</v>
+        <v>3.425584404104697</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.899732762196948</v>
+        <v>5.912711904595412</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.708112893926121</v>
+        <v>6.72122369830106</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.33215415824111</v>
+        <v>6.345197054535475</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8.941023134571523</v>
+        <v>8.954089388871999</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.463738725689019</v>
+        <v>7.476919734984257</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.402738839506718</v>
+        <v>7.415937578461481</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.899415001280133</v>
+        <v>7.912820128932964</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.694661676962554</v>
+        <v>7.708118970672771</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9.749246854510005</v>
+        <v>9.762699143230115</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.972089886662744</v>
+        <v>6.985645933014347</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.221811218939031</v>
+        <v>7.211381583240879</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>400</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.7434383202099824</v>
+        <v>-0.7309160305343596</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4.894988066825768</v>
+        <v>4.907897876401819</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.000119360229171</v>
+        <v>3.013126491646773</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.630372492836678</v>
+        <v>4.643351635235142</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.841951277764515</v>
+        <v>5.855062082139455</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.639393215480176</v>
+        <v>6.652436111774541</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.30465949820789</v>
+        <v>7.317725752508366</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.587476099426397</v>
+        <v>6.600657108721634</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.276476213244088</v>
+        <v>7.289674952198851</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.92635102821616</v>
+        <v>7.939756155868992</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.721597703898581</v>
+        <v>7.735054997608799</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>7.755980861244012</v>
+        <v>7.769433149964122</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.835726250299111</v>
+        <v>6.849282296650713</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.835447582575391</v>
+        <v>6.825017946877239</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>504</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3108986376702916</v>
+        <v>-0.2983763479946688</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.418797590635293</v>
+        <v>5.431707400211344</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.039801899911716</v>
+        <v>3.052809031329318</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.757356619820804</v>
+        <v>4.770335762219268</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.409411595224825</v>
+        <v>5.422522399599764</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.302091628178573</v>
+        <v>6.315134524472938</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>6.018945212493598</v>
+        <v>6.032011466794074</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5.551761813712098</v>
+        <v>5.564942823007335</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.689174625942492</v>
+        <v>5.702373364897255</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>6.823176425041552</v>
+        <v>6.836581552694383</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>7.015248497549372</v>
+        <v>7.02870579125959</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.454393559656708</v>
+        <v>6.467845848376818</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.438900853473719</v>
+        <v>5.452456899825322</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.696558693686512</v>
+        <v>4.68612905798836</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>635</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.3278782942100946</v>
+        <v>0.3404005838857174</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.979760437312429</v>
+        <v>3.901628283925334</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.261125649537355</v>
+        <v>2.185026020689172</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.492007712962462</v>
+        <v>3.504986855360926</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.211448133110416</v>
+        <v>4.224558937485355</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.194424662021049</v>
+        <v>4.207467558315415</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.95245824034626</v>
+        <v>3.965524494646736</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.207554839583871</v>
+        <v>4.127386668470059</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.09143684316534</v>
+        <v>5.104635582120103</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.343673862861834</v>
+        <v>5.357078990514665</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>5.926322113347403</v>
+        <v>5.939779407057621</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.858343065968427</v>
+        <v>4.871795354688537</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.595568769984148</v>
+        <v>4.609124816335751</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.057888527457287</v>
+        <v>4.047458891759135</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>810</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.1008002834001616</v>
+        <v>-0.08827799372453882</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.406044577882277</v>
+        <v>2.349615667812856</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.080685165887232</v>
+        <v>2.024183002703289</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.526924216974614</v>
+        <v>2.469919900917795</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.973724676779291</v>
+        <v>2.98683548115423</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.095928357280414</v>
+        <v>3.0379040920701</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.011194640008135</v>
+        <v>3.024260894308611</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.862167457451086</v>
+        <v>2.803801375059479</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.282649052750266</v>
+        <v>4.295847791705029</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.296721398586534</v>
+        <v>4.310126526239365</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4.832708815009696</v>
+        <v>4.846166108719913</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.249808021737842</v>
+        <v>4.263260310457952</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.199923781163307</v>
+        <v>4.213479827514909</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.708904372698854</v>
+        <v>3.698474737000701</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>1018</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5403133202099752</v>
+        <v>-0.5277910305343525</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.515711429484611</v>
+        <v>1.474304126401819</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.566655563751688</v>
+        <v>1.524856696925369</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.751822052092308</v>
+        <v>1.709887838757652</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.739010101293914</v>
+        <v>2.695659535616436</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.191159653164171</v>
+        <v>3.147534150990218</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.204561362781</v>
+        <v>3.217627617081476</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.892485922609104</v>
+        <v>2.848694400183852</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.010267961770609</v>
+        <v>4.023466700725372</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.240692874974506</v>
+        <v>4.254098002627337</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.920025994664783</v>
+        <v>4.933483288375001</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.070322708002358</v>
+        <v>4.083774996722468</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.650068097057456</v>
+        <v>3.663624143409059</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.015702985325888</v>
+        <v>3.005273349627736</v>
       </c>
     </row>
     <row r="15">
@@ -4379,46 +4379,46 @@
         <v>1224</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1820027970956204</v>
+        <v>-0.1694805074199977</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.008624430462135</v>
+        <v>0.9768354270911956</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.227170538133322</v>
+        <v>1.19494467346496</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.402730216413914</v>
+        <v>1.370402813139286</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.560624996234807</v>
+        <v>1.527826309781723</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.904051195936198</v>
+        <v>1.871109830244833</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.435873842136175</v>
+        <v>2.402416306254295</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.50468653988316</v>
+        <v>2.470869007662138</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.388721111203274</v>
+        <v>3.354112146326088</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3.485174557627921</v>
+        <v>3.449960237501649</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.0157153509574</v>
+        <v>4.029172644667618</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>3.723301122681917</v>
+        <v>3.736753411402027</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.894549779710871</v>
+        <v>2.908105826062474</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.490676340745331</v>
+        <v>2.480246705047179</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>1433</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.48234261979389</v>
+        <v>-0.5058640554823768</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1147274085385632</v>
+        <v>-0.1392588503665593</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5415473064374936</v>
+        <v>-0.5659852363199107</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.1821445567699698</v>
+        <v>0.1572405241240276</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2379874390996974</v>
+        <v>0.2127757722019936</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.7129840296764129</v>
+        <v>0.6875543315241828</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.223879553918195</v>
+        <v>1.19803194596696</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.492528364234751</v>
+        <v>1.4662559945155</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.959181931514664</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.265499667434582</v>
+        <v>2.238221985715569</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.549232037464527</v>
+        <v>2.562689331174745</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.374264182946739</v>
+        <v>2.387716471666849</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.302927925107198</v>
+        <v>2.316483971458801</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.785028880551678</v>
+        <v>1.774599244853526</v>
       </c>
     </row>
     <row r="17">
@@ -4483,46 +4483,46 @@
         <v>1623</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4713794966805622</v>
+        <v>-0.4907139484767953</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4014258350661137</v>
+        <v>0.3809370920880895</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.573500271672664</v>
+        <v>-0.5935565249074841</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5943052235537536</v>
+        <v>-0.6143170764213011</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.669719483906249</v>
+        <v>-0.6899041548157427</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2160155122395651</v>
+        <v>-0.2363845270461056</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4092105437183449</v>
+        <v>0.3884079897548389</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.6528607148109984</v>
+        <v>0.631714919299732</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.118840745263796</v>
+        <v>1.097367259891158</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.41248781194998</v>
+        <v>1.390495072125155</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.700648843763027</v>
+        <v>1.714106137473244</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.365346234010495</v>
+        <v>1.378798522730605</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.561234568228876</v>
+        <v>1.574790614580479</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.318041544374537</v>
+        <v>1.307611908676385</v>
       </c>
     </row>
     <row r="18">
@@ -4535,46 +4535,46 @@
         <v>1846</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2828420032401553</v>
+        <v>0.2669287970518539</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.6954195662863896</v>
+        <v>0.6787873642724378</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.4254068135430771</v>
+        <v>-0.4415660649875193</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1579644402086799</v>
+        <v>-0.1742414570476427</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6130730334186296</v>
+        <v>-0.6292791705603378</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.178174352087396</v>
+        <v>-0.1945384965452917</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.179385931754247</v>
+        <v>-0.1957877610051497</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3028440647943498</v>
+        <v>0.2860275792462303</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5425834141103536</v>
+        <v>0.5256056881295876</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.02277573027466</v>
+        <v>1.005267796367093</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.034707129684058</v>
+        <v>1.048164423394276</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.01491910609775</v>
+        <v>1.02837139481786</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.028033942606797</v>
+        <v>1.0415899889584</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.6818722846338972</v>
+        <v>0.671442648935745</v>
       </c>
     </row>
     <row r="19">
@@ -4587,46 +4587,46 @@
         <v>2031</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3958858717586793</v>
+        <v>0.3825200928136638</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3780845881388473</v>
+        <v>0.364313155539925</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9214492672218029</v>
+        <v>-0.9346932045805616</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4216137749416475</v>
+        <v>-0.4350797373138775</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.6882253660038913</v>
+        <v>-0.7017059414015065</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3641659401408432</v>
+        <v>-0.3777405319938651</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4713719359767836</v>
+        <v>-0.4849252047817671</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2730890111387225</v>
+        <v>-0.286867449235146</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.0370465180621764</v>
+        <v>0.02309018561408038</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.7881316479898999</v>
+        <v>0.7735811312868819</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.8574244755521221</v>
+        <v>0.8427775750805182</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.067649989752134</v>
+        <v>1.052897716893256</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.041290011992857</v>
+        <v>1.054846058344459</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.8971167110835196</v>
+        <v>0.8866870753853675</v>
       </c>
     </row>
     <row r="20">
@@ -4639,46 +4639,46 @@
         <v>2226</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.1663739283371939</v>
+        <v>0.1553663644611873</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.4119827000994789</v>
+        <v>0.4005219264688691</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6743772840661251</v>
+        <v>-0.6854423813406996</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.1171655555071069</v>
+        <v>-0.1284604453017693</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.04045105385048942</v>
+        <v>0.02896539458349423</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.2281028928995212</v>
+        <v>0.2165874776500445</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.2127724520402552</v>
+        <v>0.2012382973112352</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2186420187089055</v>
+        <v>0.2069995560546545</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.04182795903047065</v>
+        <v>-0.05337437515540699</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.8832630569414732</v>
+        <v>0.8711155098393846</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.063313015977613</v>
+        <v>1.051033453623162</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.482845191881928</v>
+        <v>1.470376122573015</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.421979619571346</v>
+        <v>1.435535665922949</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.312311913213314</v>
+        <v>1.301882277515162</v>
       </c>
     </row>
     <row r="21">
@@ -4691,46 +4691,46 @@
         <v>2417</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4307791427224785</v>
+        <v>0.4215129525862764</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.4479340907235851</v>
+        <v>0.4383756358746353</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.5015294443874794</v>
+        <v>-0.5107713245872603</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5139574040705455</v>
+        <v>-0.5231776310467993</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4526031776810342</v>
+        <v>-0.4619482271389046</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.03239775530682465</v>
+        <v>0.02289815797915651</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.0528015295869082</v>
+        <v>0.04327259526527882</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.02128444308603861</v>
+        <v>0.01168105587273516</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1408791586567375</v>
+        <v>-0.1504324414401452</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8920393291669626</v>
+        <v>0.8819049161995736</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9176274805735218</v>
+        <v>0.9074402807836606</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.513531543908471</v>
+        <v>1.503097335241215</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.217397743886202</v>
+        <v>1.230953790237805</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.260251057958108</v>
+        <v>1.249821422259956</v>
       </c>
     </row>
     <row r="22">
@@ -4743,46 +4743,46 @@
         <v>2632</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.4009998182690282</v>
+        <v>0.3935166472266118</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.3234513522156277</v>
+        <v>0.3157677212750656</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4673172168249664</v>
+        <v>-0.4747614720171072</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4302335677693776</v>
+        <v>-0.4376782776766319</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.5313908973018115</v>
+        <v>-0.5388773117999435</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1754286192431067</v>
+        <v>-0.1830129219503647</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1017774352575671</v>
+        <v>0.09407146896022311</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.1485534894112206</v>
+        <v>0.1407594978001256</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.2223965168494004</v>
+        <v>0.2145611433976384</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.7220989401371938</v>
+        <v>0.7139497042560876</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4629573696790601</v>
+        <v>0.4548727652625573</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.8228501621558593</v>
+        <v>0.8146287443431603</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.554571235101541</v>
+        <v>0.568127281453144</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.6143229625146134</v>
+        <v>0.6038933268164612</v>
       </c>
     </row>
     <row r="23">
@@ -4795,46 +4795,46 @@
         <v>2823</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.2941410728740053</v>
+        <v>0.2880434050917557</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.395517540881535</v>
+        <v>0.3891963943975867</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3332139731041579</v>
+        <v>-0.3393267381449689</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.3604434732530493</v>
+        <v>-0.3665353704145744</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.13773070103408</v>
+        <v>-0.1439665296584991</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.03767882877108519</v>
+        <v>0.03141137679219952</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.3258759055629099</v>
+        <v>0.319493161486804</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.3026335101090893</v>
+        <v>0.2962016631770794</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1551032479220709</v>
+        <v>0.1487128015090704</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5989173998975801</v>
+        <v>0.5922685408654473</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2725892053150076</v>
+        <v>0.2660284489362397</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.6458143716938878</v>
+        <v>0.6391215352332438</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.3672529948970578</v>
+        <v>0.3808090412486607</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.5815510186363255</v>
+        <v>0.5711213829381734</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2991</v>
+        <v>2992</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.5202146934430445</v>
+        <v>0.5150892956973365</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.4919234432414896</v>
+        <v>0.4866524551563955</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.317941286222009</v>
+        <v>-0.3229827688462308</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.4029608404966609</v>
+        <v>-0.4079645926888773</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2898426535459251</v>
+        <v>-0.2949379178605511</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1409603535658661</v>
+        <v>-0.1460800602828201</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1595143530627396</v>
+        <v>0.1542834576451213</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.211307875127325</v>
+        <v>0.2060124640769772</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.03153714234856864</v>
+        <v>-0.03676029479714771</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.4727772139209065</v>
+        <v>0.4673020657187408</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1198603166617005</v>
+        <v>0.1144805153108734</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.5741626794258323</v>
+        <v>0.5686312789317114</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.421287747625307</v>
+        <v>0.4348437939769099</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.5229266865540012</v>
+        <v>0.5268896046312506</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3172</v>
+        <v>3173</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.3331948456191753</v>
+        <v>0.3291310652270312</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.1519783275860505</v>
+        <v>0.1478476251455376</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6343872393937033</v>
+        <v>-0.6383029774075695</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4872005973865186</v>
+        <v>-0.4911549643877393</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4111933763235385</v>
+        <v>-0.4152145604257811</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2538908361083827</v>
+        <v>-0.2579412467160296</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.02460915207824854</v>
+        <v>0.02046246216549719</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.07911187665167319</v>
+        <v>-0.08326359612419054</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.3116849958239243</v>
+        <v>-0.3157704365326595</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.2728077211295457</v>
+        <v>0.2684715211082818</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.00871105476556977</v>
+        <v>-0.01297649845419357</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.4846288284674571</v>
+        <v>0.4802081972230994</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.3165015418213315</v>
+        <v>0.3300575881729344</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.5211348461315097</v>
+        <v>0.5242773228621189</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3329</v>
+        <v>3330</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.4688597049246681</v>
+        <v>0.4655392491545456</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.0703846546737168</v>
+        <v>0.06708399249996688</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4280243523456733</v>
+        <v>-0.4312015538485809</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.401373538909354</v>
+        <v>-0.404552556381617</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6540043843085925</v>
+        <v>-0.6571421706308413</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.310337081193488</v>
+        <v>-0.3135614915807707</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.01908150898635341</v>
+        <v>-0.02240010904392875</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.009889892529834299</v>
+        <v>0.006532408481817242</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1845315851962255</v>
+        <v>-0.1878362921789574</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1519735904723873</v>
+        <v>0.1485144042193269</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.02411871230194151</v>
+        <v>0.02068356046508057</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.3155725754439516</v>
+        <v>0.3120501967828559</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.06245297702584196</v>
+        <v>0.05897908440213939</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.1189411241794858</v>
+        <v>0.1215644934237972</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3436</v>
+        <v>3437</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4494436745711212</v>
+        <v>0.4466202013497025</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1293268139255304</v>
+        <v>0.1265119674427027</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3078295808790372</v>
+        <v>-0.3105394016246805</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3069461374593203</v>
+        <v>-0.3096509757309107</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6264812331208347</v>
+        <v>-0.6291224796713522</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.2842420923014757</v>
+        <v>-0.2869688229134155</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.004663766386933332</v>
+        <v>-0.007477499524156883</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.09604669791564646</v>
+        <v>0.09317816593917172</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.03607827672975361</v>
+        <v>-0.03891307801613664</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.2054207956580214</v>
+        <v>0.2024704830994466</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.07518886411957482</v>
+        <v>0.07226429993438188</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.4168301922504156</v>
+        <v>0.4138065143142171</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.1876319820419141</v>
+        <v>0.1846516974651422</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1919667909572453</v>
+        <v>0.1941625497285671</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3579</v>
+        <v>3580</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1791674704358996</v>
+        <v>0.1770299755886597</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.225258186569576</v>
+        <v>0.2230426425488119</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1266215868460279</v>
+        <v>-0.1287559923409702</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.06480722296159769</v>
+        <v>-0.06695477145009932</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2815158348330371</v>
+        <v>-0.2836255745894505</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.0869120334338831</v>
+        <v>0.08471035926616821</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.3241798551515629</v>
+        <v>0.3219075200020995</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2907536447541403</v>
+        <v>0.2884708287439395</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.02201192752979608</v>
+        <v>0.01980047521140449</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2199597360029273</v>
+        <v>0.2176579415832833</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1146741974775907</v>
+        <v>0.1123924243461687</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3323561754020687</v>
+        <v>0.3300138311478165</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.1793016692935296</v>
+        <v>0.1769840559358329</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.05373481364553356</v>
+        <v>0.05546487425154822</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3699</v>
+        <v>3700</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1735875418589856</v>
+        <v>0.1719253376315493</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.408596258687794</v>
+        <v>0.4068202901949221</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.2171004923046453</v>
+        <v>0.2153630855567741</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.173375997824543</v>
+        <v>0.1716535220275901</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.10761722277487</v>
+        <v>-0.1092814066715562</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2046076746115446</v>
+        <v>0.2028676112351562</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.4044975985856496</v>
+        <v>0.4027001253165707</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.3300536972671395</v>
+        <v>0.3282609943125578</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.0680528871101842</v>
+        <v>0.06632812358886042</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1240285869523206</v>
+        <v>0.1222615554370279</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.09653017283429222</v>
+        <v>0.09476334219426974</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.2812443035569032</v>
+        <v>0.2794277474789766</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.1465370611099175</v>
+        <v>0.1447429829517191</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.08720481425963555</v>
+        <v>0.08853146039076165</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3775</v>
+        <v>3776</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.01448142635813809</v>
+        <v>0.01314572718536056</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.2916080826694483</v>
+        <v>0.2901576440892555</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2808906227754022</v>
+        <v>0.2794322745884159</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.1349960067072189</v>
+        <v>0.13357878790287</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.007384681570002272</v>
+        <v>0.005986784913559973</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2664748966855655</v>
+        <v>0.2650153929584675</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.4077795405135447</v>
+        <v>0.4062798101345919</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2725461867048793</v>
+        <v>0.2710695888908532</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.01188357511570359</v>
+        <v>-0.01328722711878783</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.131696357668396</v>
+        <v>0.1302323463451813</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.1271032623951385</v>
+        <v>0.1256345159999057</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2028964026790163</v>
+        <v>0.2014077396941403</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1683533689431727</v>
+        <v>0.1668623866692514</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.1417389733038732</v>
+        <v>0.1428145570467407</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3858</v>
+        <v>3859</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.05112380843895892</v>
+        <v>0.05007570500283975</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.3652723045518655</v>
+        <v>0.3641107412946099</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.1654075483914994</v>
+        <v>0.1642892823444484</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.02629762091720522</v>
+        <v>-0.02736431203805978</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1369083033060932</v>
+        <v>-0.1379575662576613</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.07123491232444934</v>
+        <v>0.07013717202796244</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.2076349186477344</v>
+        <v>0.2064996790474254</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1946189565692507</v>
+        <v>0.1934772898341777</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.1109170044623653</v>
+        <v>-0.1119813625009414</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.01128111625344985</v>
+        <v>0.01016775307324025</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.101246118945248</v>
+        <v>-0.1023349557832276</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.02640255844510619</v>
+        <v>-0.0275106469796782</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.06026628657793509</v>
+        <v>0.05912685623619751</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.03819160871542238</v>
+        <v>-0.03731685488486391</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3928</v>
+        <v>3929</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1074244049866735</v>
+        <v>0.1066029953408432</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.4381352749475909</v>
+        <v>0.4372051588174486</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2348235998839101</v>
+        <v>0.2339386743879004</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.09964623585343446</v>
+        <v>0.09879717978959945</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.06933904481613951</v>
+        <v>-0.07015376346745938</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1404094756427696</v>
+        <v>0.1395455859934813</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1712414550058554</v>
+        <v>0.1703680289311365</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1501349708041175</v>
+        <v>0.1492593958880803</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.04935648444214991</v>
+        <v>-0.05018269904670092</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.02074968388964038</v>
+        <v>-0.02159650113583211</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.08404971406122286</v>
+        <v>-0.08488396475132021</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.0099224466440333</v>
+        <v>-0.01077544835691668</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.06771912380381906</v>
+        <v>0.06683954855911622</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.02453205082581889</v>
+        <v>-0.02386217529124934</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3983</v>
+        <v>3984</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.05911423234257995</v>
+        <v>0.05848852288070816</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.2379167276517933</v>
+        <v>0.237227205731152</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1320672821120041</v>
+        <v>0.131399332698102</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1006955582010676</v>
+        <v>0.1000366627764464</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.02682101724346353</v>
+        <v>0.0261740280447782</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.06240749761497</v>
+        <v>0.06175474904907929</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.04150160347105469</v>
+        <v>0.04085278833898798</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.01085681609128386</v>
+        <v>-0.01149827974955286</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1332529743186015</v>
+        <v>-0.1338647820703827</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1167891774522616</v>
+        <v>-0.1174153586746414</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2071529232965972</v>
+        <v>-0.2077591483656178</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.008134571629263121</v>
+        <v>-0.008790633277222071</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.06263388082119548</v>
+        <v>0.06195481860805785</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.05000308275224796</v>
+        <v>-0.04948004509062542</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4022</v>
+        <v>4023</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1459668842509885</v>
+        <v>0.1454467048472168</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.23311399642418</v>
+        <v>0.2325571081242472</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1492639176306199</v>
+        <v>0.1487239135605094</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1442613817255634</v>
+        <v>0.1437235667997356</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1651341108084168</v>
+        <v>0.1645858916632577</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1288473097729721</v>
+        <v>0.1283105846100554</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1073400641051308</v>
+        <v>0.106807638364451</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.100633994163239</v>
+        <v>0.1000986574930351</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.00369250328630244</v>
+        <v>0.003180413966482831</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.01179563825093055</v>
+        <v>0.01127341437408091</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.02995509113247863</v>
+        <v>-0.03046909578414869</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1426607817211476</v>
+        <v>0.1421039574175396</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.2087066132123638</v>
+        <v>0.2081292151397847</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.09961963628002479</v>
+        <v>0.09999930407337132</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4073</v>
+        <v>4074</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1252596729373607</v>
+        <v>0.1249073117705137</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1667138930191641</v>
+        <v>0.1663413418937409</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.05447783231537073</v>
+        <v>0.05413016361740119</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.05114153520748488</v>
+        <v>0.05079531789920111</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1384970886415289</v>
+        <v>0.1381260057250486</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.008359155200821533</v>
+        <v>0.008021609079776226</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.08407126291377409</v>
+        <v>0.08371448076124466</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1451495488012426</v>
+        <v>0.1447747557804533</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1222339376187804</v>
+        <v>0.1218642142728896</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1686860784982258</v>
+        <v>0.168299559498216</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1249343084128114</v>
+        <v>0.1245570824751283</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2958581618575096</v>
+        <v>0.2954390380897394</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.3803997898180072</v>
+        <v>0.3799571432764779</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.2512958516645227</v>
+        <v>0.2515029738777343</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/volatility/vol_ratio_7_21.xlsx
+++ b/workspaces/btc_daily_14days/volatility/vol_ratio_7_21.xlsx
@@ -575,46 +575,46 @@
         <v>57</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1499484065002648</v>
+        <v>0.1208514989448162</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14.28625824928604</v>
+        <v>14.28519135926694</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.647288945656328</v>
+        <v>8.647200758937146</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.02942272635277</v>
+        <v>14.0290249346714</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15.24621235739014</v>
+        <v>15.29474104914508</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>17.29787609425895</v>
+        <v>17.3218783384859</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22.47165242269371</v>
+        <v>22.51968486845338</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>22.01079629293246</v>
+        <v>22.0600581954584</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>18.45091854623199</v>
+        <v>18.52414514693691</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>14.10110115215043</v>
+        <v>14.20038597736878</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>15.65311756421488</v>
+        <v>15.75298162503105</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>17.44489758013518</v>
+        <v>17.56855527132294</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>17.02921372566014</v>
+        <v>17.17787720992225</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>19.01361443810452</v>
+        <v>19.18561319767198</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>68</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.007255438975726</v>
+        <v>-1.036359719972133</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.64872988648866</v>
+        <v>7.647614654278854</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.257220935117523</v>
+        <v>7.257126155884229</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.388784685118942</v>
+        <v>7.388346412780095</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.386277423216391</v>
+        <v>5.43474630149894</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.619837480469471</v>
+        <v>8.643795418821242</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17.34534413783669</v>
+        <v>17.39335546909776</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>15.41503094481205</v>
+        <v>15.46426838757052</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>15.35813223907923</v>
+        <v>15.43134903100427</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>14.51303448351733</v>
+        <v>14.61231973369263</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.84270278510594</v>
+        <v>12.94256056611815</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>18.75974429477953</v>
+        <v>18.88340337519484</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>13.93388687018641</v>
+        <v>14.08254773135378</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>12.69266500570144</v>
+        <v>12.8646637652681</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>88</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-9.268087108797587</v>
+        <v>-9.297266819944852</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.080486156845438</v>
+        <v>-4.081699026999729</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.05764841542979582</v>
+        <v>0.05750024353454108</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.587690401048484</v>
+        <v>3.587228698198764</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.319067863775999</v>
+        <v>5.367534678820547</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.349286470630965</v>
+        <v>3.373215519394329</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.131025200520966</v>
+        <v>2.178961872139148</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.738421048475779</v>
+        <v>-1.689256889618363</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.93448592949818</v>
+        <v>-2.861335703981283</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.3785592441306278</v>
+        <v>-0.2793185607639899</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.718579611488494</v>
+        <v>-1.618754824300026</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.684602446459451</v>
+        <v>-1.560973836406319</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-8.921302892369859</v>
+        <v>-8.77265958244589</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.561345689486387</v>
+        <v>-7.389346929920244</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>103</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.849558241324758</v>
+        <v>2.820496678543506</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>7.049612272022713</v>
+        <v>7.048499764015205</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.817674328941862</v>
+        <v>1.817541550522144</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.9793727247037012</v>
+        <v>0.978893985948325</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.348267880638488</v>
+        <v>3.396718917449412</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.5213907019223</v>
+        <v>7.54534532185167</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.593287581523477</v>
+        <v>2.641223690318242</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.066613786943606</v>
+        <v>4.115800461671903</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6.915761582620732</v>
+        <v>6.988944136728549</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.008358686158473</v>
+        <v>8.107620017043786</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.806078533899296</v>
+        <v>7.905921144207767</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.020424298303261</v>
+        <v>2.144055139790765</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.454237952194916</v>
+        <v>6.602890539723084</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.710940276974327</v>
+        <v>5.882939036540989</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>104</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.360674695336272</v>
+        <v>1.331606425966683</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>7.420485407387673</v>
+        <v>7.419384679116135</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.19480931650736</v>
+        <v>3.194691143806459</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.243068537715402</v>
+        <v>5.242626254401962</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.748179452360802</v>
+        <v>3.796629656456851</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.005400223569445</v>
+        <v>5.029341068129931</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.08351780809393</v>
+        <v>1.131442009359986</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.57775279051782</v>
+        <v>1.626925032686081</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.4030108939307482</v>
+        <v>-0.3298608918744179</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.589952747060352</v>
+        <v>2.689192983165142</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.307827317040179</v>
+        <v>4.40765875100643</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.46052990994761</v>
+        <v>1.584156362969225</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.07985129941909719</v>
+        <v>0.2284968783983459</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.540366668507367</v>
+        <v>-3.368367908940705</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.79700704467384</v>
+        <v>2.724727729265787</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.877058822530941</v>
+        <v>-1.859638996758449</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.111890053971187</v>
+        <v>-1.506945571491848</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.329797752870022</v>
+        <v>-2.125652362640921</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3474383535960825</v>
+        <v>-1.117033402358295</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.856955656118323</v>
+        <v>-4.5942931174527</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.943419529391058</v>
+        <v>-4.656731101235053</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.3654254115513</v>
+        <v>-2.123474019510198</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.799992902382847</v>
+        <v>1.593862362813518</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.3356243209808198</v>
+        <v>-1.487501221572245</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.748074291382238</v>
+        <v>0.5614890529410772</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.268477244081247</v>
+        <v>-2.386706146577176</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.363971391916635</v>
+        <v>0.2212038196202073</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.590285122449764</v>
+        <v>0.8898738493012246</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.647639221171602</v>
+        <v>-1.656925433957042</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.268934254948412</v>
+        <v>-3.237301661202089</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.462617106484529</v>
+        <v>1.439712981709867</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.255173458852866</v>
+        <v>-1.248025040302871</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.488522342730278</v>
+        <v>-1.736628217773664</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.190320653826547</v>
+        <v>-1.464642115436334</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3970031517400372</v>
+        <v>-0.9613369895520663</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.004536365427263</v>
+        <v>-2.554921434463132</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.357855679107374</v>
+        <v>0.7932575122198955</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5095514257323899</v>
+        <v>-0.02940590399995813</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.8762400206090319</v>
+        <v>0.3313692679047406</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.05344409826246</v>
+        <v>1.519565545678724</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.776800817556165</v>
+        <v>2.255033991321319</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.432160804019979</v>
+        <v>1.939107101923874</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.247505422565801</v>
+        <v>-2.262137217724316</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.943151395316782</v>
+        <v>-1.935155652460899</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4196338581718919</v>
+        <v>-0.4202629172346946</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.248510085527023</v>
+        <v>-1.245112596347923</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.570960049814232</v>
+        <v>1.607151175963125</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.567374523501208</v>
+        <v>3.312319859434353</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.962743931597046</v>
+        <v>3.730678577613546</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.017923642069618</v>
+        <v>2.789292533026455</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.956562165506334</v>
+        <v>2.753068736402447</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.029593349440752</v>
+        <v>3.843222784881405</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.267445041382764</v>
+        <v>5.07510319995253</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.382060411735743</v>
+        <v>3.221965525701066</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.521577636757307</v>
+        <v>1.392708686533808</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3057871776465859</v>
+        <v>0.2063468499847971</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.604704277962689</v>
+        <v>1.551277040991039</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.474802626681289</v>
+        <v>-1.457759838497317</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4186205894799357</v>
+        <v>-0.420294357985135</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2862456078681319</v>
+        <v>-0.2908169531702711</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.222132238459942</v>
+        <v>-4.119700045762265</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.404109673429723</v>
+        <v>-4.326230859565342</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.580463674713116</v>
+        <v>-1.522922964271082</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.6328397314255199</v>
+        <v>0.4002538983580166</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.08912381166805261</v>
+        <v>-0.1144939352938223</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.5018067665418684</v>
+        <v>-0.9372226947078985</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4407938475254838</v>
+        <v>-1.141311384296301</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.01964261653476</v>
+        <v>1.308555285363724</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.8255668714999729</v>
+        <v>-1.478104710595495</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1143024414722689</v>
+        <v>-0.7505909490585978</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>209</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.49030946270473</v>
+        <v>-2.76373134175703</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-6.716649632395736</v>
+        <v>-6.739746056563327</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-10.93473815032291</v>
+        <v>-11.43092433415863</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-6.981158430363763</v>
+        <v>-7.008780738898921</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-7.518923778678143</v>
+        <v>-7.503533602047099</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-6.266113619336146</v>
+        <v>-6.275349430919412</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-5.872993584152582</v>
+        <v>-5.85933834555437</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.427842013373336</v>
+        <v>-4.418839299944828</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.400857168468846</v>
+        <v>-6.585478899801153</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.860163707802926</v>
+        <v>-5.023938739773428</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-6.020825200551556</v>
+        <v>-5.707556099621321</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.509892698391084</v>
+        <v>-5.172732173304716</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.148312800314613</v>
+        <v>-0.999635811073631</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.357996407189738</v>
+        <v>-2.185997647622976</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>190</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3748916389466714</v>
+        <v>-0.1548715235902804</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>4.324022785500837</v>
+        <v>4.55467672865484</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.8013849851485375</v>
+        <v>-1.087436515099185</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-6.454353461828845</v>
+        <v>-6.207434871542922</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.51773006648984</v>
+        <v>-7.751185186108316</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-7.220962652080303</v>
+        <v>-6.954262449785276</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-5.728765329609274</v>
+        <v>-5.439813648383783</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.669793669332932</v>
+        <v>-5.383103591676978</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.205212148041639</v>
+        <v>-4.893683627205256</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-5.002920347269026</v>
+        <v>-4.670228852305868</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-4.681927838737899</v>
+        <v>-4.584727042510778</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-6.22656303354605</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.017992197343759</v>
+        <v>-3.870449208203162</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.214455737333282</v>
+        <v>-2.04245697776674</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>223</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>5.807922627471818</v>
+        <v>5.296893374503732</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.854669145481616</v>
+        <v>2.367162676639808</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6696746394865798</v>
+        <v>0.625306292091409</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.039044532803992</v>
+        <v>2.994533887324799</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1855753671795028</v>
+        <v>-0.1850970138809984</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1110838260253146</v>
+        <v>0.09166703760294581</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.452477689893826</v>
+        <v>-4.650704609383574</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.232092672402807</v>
+        <v>-1.982052296559523</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.636827189437</v>
+        <v>-3.363097628848926</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.798781727038666</v>
+        <v>-1.500523185879963</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.794931440419347</v>
+        <v>-3.498208989537751</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.521397851644977</v>
+        <v>-1.398350049635532</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.838217421635783</v>
+        <v>-2.690368962746248</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.95861434011816</v>
+        <v>-3.786615580551498</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.547793190712021</v>
+        <v>1.726452224495944</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.779112612870776</v>
+        <v>-3.079104404309028</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.887371352695531</v>
+        <v>-5.095427130718711</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.052588275834829</v>
+        <v>-2.824431798512308</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.439107613303449</v>
+        <v>-1.190280561442272</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.216056042667326</v>
+        <v>-1.684359596782151</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.382678869460484</v>
+        <v>-2.815919191601054</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-6.011340092851476</v>
+        <v>-5.661638834652386</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4.991302724027271</v>
+        <v>-4.628861829388676</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.523840485316505</v>
+        <v>-1.415441973381647</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.189594529717787</v>
+        <v>-1.084823062629212</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.30615773725048</v>
+        <v>1.112381107890755</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.186230483537443</v>
+        <v>0.7172231813268084</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.034477406336585</v>
+        <v>2.570546118208618</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>195</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.223544443861378</v>
+        <v>-2.249678661800694</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7791658928356355</v>
+        <v>0.7770285133867674</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.922838094063991</v>
+        <v>1.922184348718147</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.077881940065218</v>
+        <v>3.07739913379595</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>7.665557818874817</v>
+        <v>7.717710566007781</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>6.42497447547202</v>
+        <v>6.452034546365176</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>7.36549609962254</v>
+        <v>7.417019482780852</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>5.360883363801726</v>
+        <v>5.412725183935741</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.8508343057444137</v>
+        <v>-0.7780935790468675</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.887206335498362</v>
+        <v>1.987821429881286</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.220219443803394</v>
+        <v>3.322142520806963</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>5.817252118372963</v>
+        <v>5.944411822274532</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5.397320060885036</v>
+        <v>5.549253895710706</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>5.626299998159297</v>
+        <v>5.798298757725838</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>191</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.537891577984396</v>
+        <v>3.753389505127849</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.8810176986938245</v>
+        <v>1.120703275258293</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.533626858072175</v>
+        <v>1.767412275021506</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.138939320210511</v>
+        <v>-4.904525868236682</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-6.200280648969446</v>
+        <v>-6.155292521654935</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.24035628940652</v>
+        <v>-2.217585536867475</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.80171789793809</v>
+        <v>-1.754681416668859</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.268548961667769</v>
+        <v>-2.220514177052202</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.282744524200034</v>
+        <v>-1.210366367341003</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.006775838720664</v>
+        <v>1.10716630838882</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.767733991686228</v>
+        <v>-0.6676547674196414</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.882645476663548</v>
+        <v>2.008313017065667</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.15353639015148</v>
+        <v>-1.004645956618646</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.6430807741023727</v>
+        <v>0.8150795336690351</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>215</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.07678881852585562</v>
+        <v>0.04688837240654919</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.068457785147622</v>
+        <v>-1.06918748594326</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.06777909251171366</v>
+        <v>-0.06791596924333021</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.5272201418292681</v>
+        <v>0.5265780730896452</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.405203716001864</v>
+        <v>-1.358019905071572</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.502866235208955</v>
+        <v>-2.480583223461899</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.6661803823329748</v>
+        <v>0.7145746408010112</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.593847539352723</v>
+        <v>1.644090717626966</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4.321998642903196</v>
+        <v>4.397815782908836</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.176412931041305</v>
+        <v>-1.077175588603872</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.634720692091726</v>
+        <v>-4.53712998962834</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-6.924964863588208</v>
+        <v>-6.804544647612282</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-6.879777723582265</v>
+        <v>-6.734586295106396</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-6.657540192657635</v>
+        <v>-6.485541433090972</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>191</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.171647231295367</v>
+        <v>-0.4456420579225195</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.403934778415355</v>
+        <v>1.888275196121093</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.533508145767257</v>
+        <v>1.76794144132608</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6172986075204321</v>
+        <v>0.6166791323859329</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>5.311231481478309</v>
+        <v>5.363032085674853</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.992126663503271</v>
+        <v>3.018016557373365</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.430339537887804</v>
+        <v>3.480920677571987</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.440347660450364</v>
+        <v>2.491527707764561</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.7595954164334486</v>
+        <v>-0.6868061579167417</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.086345889723475</v>
+        <v>-0.9870745293076411</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.336942533163146</v>
+        <v>-2.238335395691955</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.779886236545877</v>
+        <v>-1.656608448902922</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.19939985744805</v>
+        <v>-2.051766375466748</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1195205646782966</v>
+        <v>0.291519324244959</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>169</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.319590211207093</v>
+        <v>4.294621902923737</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.118542102620573</v>
+        <v>2.119728841436448</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.04838089166388215</v>
+        <v>-0.04915707587233697</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.100573620230428</v>
+        <v>-1.102704987320372</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.821216906406939</v>
+        <v>-2.775386080935085</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.11556492544166</v>
+        <v>-3.094316538447451</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.609451183074597</v>
+        <v>-2.563256651341483</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.302508184184809</v>
+        <v>-1.253941482730809</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.136668175421498</v>
+        <v>-3.066062020861622</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.621815366515769</v>
+        <v>-1.523026696351231</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.417019931038901</v>
+        <v>-2.318883120218615</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6097205002657162</v>
+        <v>-0.485568453859706</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.335798198693105</v>
+        <v>1.486137524901977</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.2119643016434694</v>
+        <v>-0.6316815184081648</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>181</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.755705721380721</v>
+        <v>-2.786354918809728</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.46883158563228</v>
+        <v>-5.474504379656096</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-5.861343401547835</v>
+        <v>-5.868242367970801</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.867463445789873</v>
+        <v>-1.870955011838994</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.405492279404122</v>
+        <v>-2.36020415279085</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.108726595225818</v>
+        <v>-2.087418633971986</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.194045299948783</v>
+        <v>-2.14807472319751</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-4.868556652358009</v>
+        <v>-4.823852234961997</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.928669743942528</v>
+        <v>-4.860824844098929</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.01939378761157</v>
+        <v>-2.922222485687264</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.119200353893831</v>
+        <v>-2.021390557532804</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.9821871784001388</v>
+        <v>-0.8582514444773111</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.401555873269103</v>
+        <v>-1.253409371041137</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4810952949434792</v>
+        <v>0.6530940545101416</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.242524235095331</v>
+        <v>3.186090706758627</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.568878909427845</v>
+        <v>-1.561643340422584</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.752038133615194</v>
+        <v>3.740821202908251</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.337722508996457</v>
+        <v>1.339059674502671</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-5.571931755149464</v>
+        <v>-5.479303390499844</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.448379769157228</v>
+        <v>-1.409049517250573</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.8916255478624251</v>
+        <v>-0.8367942140709346</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.821497278745319</v>
+        <v>1.861929987571045</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.39099793252214</v>
+        <v>2.457868770839411</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.274117049903502</v>
+        <v>-2.163428164406056</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.6994353027728195</v>
+        <v>0.7969883500832395</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-3.07750681205188</v>
+        <v>-2.942313266982246</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-5.414299569216588</v>
+        <v>-5.23620537076129</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-8.017338741020772</v>
+        <v>-8.15171747077121</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>107</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1444674324035162</v>
+        <v>-0.1736632267561475</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.982664231542003</v>
+        <v>1.981477445097347</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.457051725291748</v>
+        <v>3.456898335287427</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.652697429627771</v>
+        <v>2.652202937249768</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.2452489980272929</v>
+        <v>0.2937949177930648</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.5426230276624366</v>
+        <v>0.5665804366120497</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.4579126683962116</v>
+        <v>0.5059243473865322</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.794582342366482</v>
+        <v>2.843829904760199</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.602759064348376</v>
+        <v>4.676016174128073</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.883681389513846</v>
+        <v>1.98302871480842</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.678980231253654</v>
+        <v>1.778888267272329</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.582517262113647</v>
+        <v>3.706213883141892</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.096945848052535</v>
+        <v>4.245635395830362</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.453522619774496</v>
+        <v>2.625521379341158</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>143</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-6.327069876688157</v>
+        <v>-6.356265671040788</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.551254519758466</v>
+        <v>2.55006773331381</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.254385232905484</v>
+        <v>4.254231842901163</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.783211775095246</v>
+        <v>5.782717282717243</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>8.042125019202388</v>
+        <v>8.090670938968159</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>9.038799748138167</v>
+        <v>9.062757157087781</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.254788689571306</v>
+        <v>8.302800368561627</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.99051724858176</v>
+        <v>5.039764810975477</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.433031595555498</v>
+        <v>1.506288705335194</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.5831127992256384</v>
+        <v>0.6824601245202118</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.077712340266096</v>
+        <v>1.177620376284771</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.685112304581367</v>
+        <v>-1.561415683553122</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.007361059992682328</v>
+        <v>0.1413284877851453</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.278128906269643</v>
+        <v>-3.106130146702981</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>120</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.01908396946560487</v>
+        <v>-0.01011182488702644</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.907897876401798</v>
+        <v>5.906711089957142</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.51312649164678</v>
+        <v>10.51297310164246</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.310018301901835</v>
+        <v>7.309523809523832</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.105062082139469</v>
+        <v>5.153608001905241</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.817725752508359</v>
+        <v>2.86573743149868</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.517323775388292</v>
+        <v>1.566571337782008</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.456341618865473</v>
+        <v>1.529598728645169</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.726910510797651</v>
+        <v>-2.627563185503078</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.4316116690578227</v>
+        <v>-0.3317036330391474</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.230566850035849</v>
+        <v>-1.106870229007605</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.8173843700159082</v>
+        <v>-0.6686948222380806</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.075017946877239</v>
+        <v>1.247016706443901</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>76</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-7.744073925271195</v>
+        <v>-7.773269719623826</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-5.407891597282358</v>
+        <v>-5.409078383727014</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.407863333752047</v>
+        <v>3.407709943747726</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.725069417396476</v>
+        <v>-1.725563909774479</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.631377871613097</v>
+        <v>5.679923791378869</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.297172953879802</v>
+        <v>3.321130362829415</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.5808836472452157</v>
+        <v>0.6288953262355363</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.517763943909912</v>
+        <v>-2.468516381516196</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.894535574116901</v>
+        <v>-3.821278464337205</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.5187035242900109</v>
+        <v>0.6180508495845842</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.629791839714066</v>
+        <v>1.729699875732742</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.598987902667417</v>
+        <v>-3.475291281639173</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.244019138755981</v>
+        <v>1.392708686533808</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.785544262666711</v>
+        <v>2.957543022233374</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>83</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.735951439345193</v>
+        <v>1.706755644992562</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.739223177606632</v>
+        <v>3.738036391161977</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-5.089283146907441</v>
+        <v>-5.089436536911762</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-7.368696557535941</v>
+        <v>-7.369191049913944</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-6.702166833523172</v>
+        <v>-6.653620913757401</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-8.814431358104947</v>
+        <v>-8.790473949155334</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-8.899141717371151</v>
+        <v>-8.85113003838083</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-3.342113975615753</v>
+        <v>-3.292866413222036</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-4.607915409246971</v>
+        <v>-4.534658299467274</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-5.457834205576759</v>
+        <v>-5.358486880282186</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-10.48181247227072</v>
+        <v>-10.38190443625204</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-10.44743431991536</v>
+        <v>-10.32373769888711</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-4.843488787686603</v>
+        <v>-4.694799239908775</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-8.232210968785402</v>
+        <v>-8.06021220921874</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>70</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.233369683751341</v>
+        <v>3.20417388939871</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.479326447830395</v>
+        <v>4.47813966138574</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.084555063075356</v>
+        <v>4.084401673071035</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.071923063806572</v>
+        <v>7.071428571428569</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>3.676490653567974</v>
+        <v>3.725036573333746</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.973864683203061</v>
+        <v>3.997822092152674</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.825131390348773</v>
+        <v>-1.777119711358452</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.292200034135512</v>
+        <v>-2.242952471741795</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.361103523627378</v>
+        <v>3.434360633407074</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.774529558416759</v>
+        <v>-1.675182233122186</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.8779121404659378</v>
+        <v>0.9778201764846131</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.9122902928211829</v>
+        <v>1.035986913849428</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.4921394395078167</v>
+        <v>0.6408289872856443</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>55</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.390006939625287</v>
+        <v>-3.419202733977919</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-14.09210212359818</v>
+        <v>-14.09328891004284</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-7.214146235625947</v>
+        <v>-7.214299625630268</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.188806180689717</v>
+        <v>0.188311688311714</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.92324390032126</v>
+        <v>6.971789820087032</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-5.506654797316372</v>
+        <v>-5.482697388366759</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-9.227728792946181</v>
+        <v>-9.17971711395586</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-11.51297925491474</v>
+        <v>-11.46373169252102</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6.119415956892006</v>
+        <v>-6.046158847112309</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.969334753221915</v>
+        <v>-6.869987427927342</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-8.992217729663928</v>
+        <v>-8.892309693645252</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1330695136005389</v>
+        <v>0.2567661346287835</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.2870813397129268</v>
+        <v>-0.1383917919350992</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.879527507668215</v>
+        <v>-1.707528748101552</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>39</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>9.057545507927188</v>
+        <v>9.028349713574556</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2459482774443345</v>
+        <v>-0.2471350638889902</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.923382901903224</v>
+        <v>1.923229511898903</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.61771060959412</v>
+        <v>4.617216117216117</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>14.33583131290872</v>
+        <v>14.38437723267449</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>6.94089765023611</v>
+        <v>6.964855059185723</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.856187290969906</v>
+        <v>6.904198969960227</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.51732377538828</v>
+        <v>11.566571337782</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>14.02044418296812</v>
+        <v>14.09370129274782</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13.17052538663826</v>
+        <v>13.26987271193283</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>18.09402935658319</v>
+        <v>18.19393739260187</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>15.56430494483592</v>
+        <v>15.68800156586416</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15.14415409152254</v>
+        <v>15.29284363930037</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>15.36988974174904</v>
+        <v>15.5418885013157</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>51</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.500523873671611</v>
+        <v>-1.529719668024242</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-5.07249428046093</v>
+        <v>-5.073681066905586</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-7.42804997894148</v>
+        <v>-7.428203368945802</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-7.297824835353133</v>
+        <v>-7.298319327731136</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-1.953761447272349</v>
+        <v>-1.905215527506577</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-9.499524672539216</v>
+        <v>-9.475567263589603</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.741097776903395</v>
+        <v>-1.693086097913074</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.674186520486337</v>
+        <v>3.723434082880054</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.495557305139997</v>
+        <v>9.568814414919693</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.5672071362611</v>
+        <v>12.66655446155568</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>12.36250597800093</v>
+        <v>12.4624140140196</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>12.39688413035628</v>
+        <v>12.52058075138452</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>13.93751759076832</v>
+        <v>14.08620713854615</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.20246892726941</v>
+        <v>12.37446768683608</v>
       </c>
     </row>
   </sheetData>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4074</v>
+        <v>4085</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.07083528671248018</v>
+        <v>-0.06989708598996458</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.004975349246734595</v>
+        <v>-0.004931575407738364</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.01930924886729457</v>
+        <v>-0.01925346085754143</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.02266207681187637</v>
+        <v>-0.02258852258852784</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.05780835626368486</v>
+        <v>-0.05889810459208888</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.03251940427820443</v>
+        <v>0.03181741517808945</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.0592106826725427</v>
+        <v>0.05781954293563274</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.02222573617260792</v>
+        <v>0.02090198228620466</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.0007148492230655279</v>
+        <v>-0.002593610393091694</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.05239686031540458</v>
+        <v>-0.05480701039915914</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.09619346940125695</v>
+        <v>-0.09850076285001563</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.121636526188972</v>
+        <v>-0.1244870628711041</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1599201573370124</v>
+        <v>-0.1633105833737076</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1412314394752343</v>
+        <v>-0.1452721552452019</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4017</v>
+        <v>4028</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.07396813971549676</v>
+        <v>-0.07259635841828782</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2077635780533882</v>
+        <v>-0.207150296181446</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1422856235468686</v>
+        <v>-0.1418919639678364</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2220568574392985</v>
+        <v>-0.2214321092478642</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2749677241198683</v>
+        <v>-0.2761665831827145</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2124707205236049</v>
+        <v>-0.2128532582649498</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2588150029588334</v>
+        <v>-0.2600370418594267</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2897853471570642</v>
+        <v>-0.2909728697869838</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2625378772392395</v>
+        <v>-0.2647644418647488</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2532306633302142</v>
+        <v>-0.2565314394713525</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.3196713705504024</v>
+        <v>-0.3228141928671917</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.3709002663085812</v>
+        <v>-0.3748603034493172</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4038287038470472</v>
+        <v>-0.4087047502599717</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.4130328372900394</v>
+        <v>-0.4188224196732691</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3949</v>
+        <v>3960</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.05789735309870991</v>
+        <v>-0.05604688655322576</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.343048854221756</v>
+        <v>-0.3420300983610716</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2697017911815038</v>
+        <v>-0.2689458104703562</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3531121182379664</v>
+        <v>-0.3521050737675395</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.372451813767583</v>
+        <v>-0.3742327640307792</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.3645590866080752</v>
+        <v>-0.3649371244371409</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.5619506883409713</v>
+        <v>-0.563176105178897</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.5602152048055586</v>
+        <v>-0.5615174166304939</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.5315187756716639</v>
+        <v>-0.5342936631160313</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.5074990933088515</v>
+        <v>-0.5118551464852743</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.5463215206098226</v>
+        <v>-0.5506034564053266</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.7003213425694099</v>
+        <v>-0.7055577605573546</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.6507177033492795</v>
+        <v>-0.6575444393381886</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.6387070467920353</v>
+        <v>-0.6469226874954899</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3861</v>
+        <v>3872</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1520215017320368</v>
+        <v>0.1539808392056798</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2578650980365964</v>
+        <v>-0.257037622710186</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2771627645515693</v>
+        <v>-0.2763650389704679</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.442930979076408</v>
+        <v>-0.4416353867667695</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.5021730599794125</v>
+        <v>-0.504727478641037</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.4492051391947101</v>
+        <v>-0.4498951390696675</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.6233290561782852</v>
+        <v>-0.6254974228452141</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.533361510362937</v>
+        <v>-0.5358869740625849</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.476750293533172</v>
+        <v>-0.4814063440054639</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5104378932901312</v>
+        <v>-0.5171400688880325</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5196033874843735</v>
+        <v>-0.5263272889531763</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.6778875852157853</v>
+        <v>-0.6861164861062363</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4622143372177518</v>
+        <v>-0.4731100042675607</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.4809261090668073</v>
+        <v>-0.4936857728949349</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3758</v>
+        <v>3769</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.0780868864637938</v>
+        <v>0.08110975099878459</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4581498689562693</v>
+        <v>-0.456684837046275</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3345784698814782</v>
+        <v>-0.3335877449183897</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4819137575461667</v>
+        <v>-0.4804559029221593</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.6077066993843161</v>
+        <v>-0.6113470007416808</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.6676647910401243</v>
+        <v>-0.6683906995565039</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.7114907149551044</v>
+        <v>-0.7147710430775902</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.659438534211418</v>
+        <v>-0.6630092361694224</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6793657068497794</v>
+        <v>-0.685557604158177</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7439227383362237</v>
+        <v>-0.7528392699628554</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.7477953081609385</v>
+        <v>-0.7567654923534377</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.7518434457805654</v>
+        <v>-0.763459992995962</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.6517818161452382</v>
+        <v>-0.6664843889932186</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.6506339956453715</v>
+        <v>-0.6679474750365912</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3654</v>
+        <v>3665</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.04158192419703255</v>
+        <v>0.04562498859860398</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6823912670788133</v>
+        <v>-0.6801803976686145</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.43503176210492</v>
+        <v>-0.4337080735479688</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.6448579717517546</v>
+        <v>-0.6428571428571459</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.7316837546063937</v>
+        <v>-0.7364301037017498</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.8291313377066274</v>
+        <v>-0.8300725832780316</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.762580174833893</v>
+        <v>-0.7671601719871504</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.7231133830816532</v>
+        <v>-0.7279896356130706</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.6872313063417295</v>
+        <v>-0.6956510442884749</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.8388113673677537</v>
+        <v>-0.850512217937009</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.8916882345487096</v>
+        <v>-0.9033139565579162</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.8148119266223119</v>
+        <v>-0.8300772101911633</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.6726055282466845</v>
+        <v>-0.6918808560624541</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.5683865413548261</v>
+        <v>-0.5913189006502293</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3523</v>
+        <v>3532</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.06087640415450579</v>
+        <v>-0.05525855174928296</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.637968488264093</v>
+        <v>-0.6357670359248644</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.4098633158277423</v>
+        <v>-0.3932945437556228</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6193890216164988</v>
+        <v>-0.5870214225198751</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.7459716193615407</v>
+        <v>-0.7220982127840401</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.7165440581971367</v>
+        <v>-0.688328152064777</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.6443031508636992</v>
+        <v>-0.6206955815030071</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.6992295125935684</v>
+        <v>-0.675441667589773</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.8169010115199669</v>
+        <v>-0.7818643181119569</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.8575219841933901</v>
+        <v>-0.8265259389213</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.9898457397706721</v>
+        <v>-0.9584721672780105</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.7979427365606924</v>
+        <v>-0.7714612281585005</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.7483340484117136</v>
+        <v>-0.7262637161603536</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.6486550590835805</v>
+        <v>-0.6470942788335634</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3348</v>
+        <v>3355</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.02206370724871931</v>
+        <v>0.02924071446555132</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.5004478762062305</v>
+        <v>-0.4985176682127701</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.50773788987334</v>
+        <v>-0.4899986665596217</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.5861565614861703</v>
+        <v>-0.5521488024460766</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.7071584841794802</v>
+        <v>-0.6685745731765493</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.6917797498831817</v>
+        <v>-0.6473720949807955</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.6572295247724966</v>
+        <v>-0.6027243358324625</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.6310011078008841</v>
+        <v>-0.5762858050751376</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.9305755697218174</v>
+        <v>-0.8649631449282751</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.9289789276632234</v>
+        <v>-0.8685796635654413</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.087386064760643</v>
+        <v>-1.026520433754115</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.9469847604836374</v>
+        <v>-0.8923291086262211</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.9325928899721632</v>
+        <v>-0.883548274796496</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.8096893410558437</v>
+        <v>-0.783534709353404</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3140</v>
+        <v>3146</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1724045922810262</v>
+        <v>0.1814651225480972</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4048802545581367</v>
+        <v>-0.4030766832452386</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.5135740805083415</v>
+        <v>-0.4946314610951887</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.5422809140337748</v>
+        <v>-0.5061127462078332</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.8580656991701474</v>
+        <v>-0.8197591509165889</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.9739148100309336</v>
+        <v>-0.9104285534908882</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.9632659830288262</v>
+        <v>-0.8906077461662818</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.8727133205311546</v>
+        <v>-0.7998731771867824</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.188067496131829</v>
+        <v>-1.105321906275421</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.257444861942716</v>
+        <v>-1.18160150454618</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.50834302975359</v>
+        <v>-1.431873052776588</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.233749536223016</v>
+        <v>-1.165656374543069</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.095162147793729</v>
+        <v>-1.034768142856898</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.8835807792374055</v>
+        <v>-0.849296071687057</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2934</v>
+        <v>2937</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.07184094700139099</v>
+        <v>0.08398786992481888</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.3297595972107104</v>
+        <v>-0.3280243238827225</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.5202408900352111</v>
+        <v>-0.4999213673090139</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5602574897222894</v>
+        <v>-0.5214334206187559</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6218701616467328</v>
+        <v>-0.5849318962272037</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.7330763158727294</v>
+        <v>-0.6673564792758526</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.9199317211041631</v>
+        <v>-0.845611532143856</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9784201810298256</v>
+        <v>-0.8852754784427788</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.277740778138231</v>
+        <v>-1.175830263761</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.310499206745916</v>
+        <v>-1.198991756931669</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.583297062316291</v>
+        <v>-1.452549725814507</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.46217447946367</v>
+        <v>-1.341723870940925</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.114090786824583</v>
+        <v>-1.003219847774382</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.9375928234022339</v>
+        <v>-0.8563200317242874</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2725</v>
+        <v>2728</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2683508316357361</v>
+        <v>0.3021599063036646</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1600972898915529</v>
+        <v>0.1631962927339217</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2785223860749255</v>
+        <v>0.3375345051512326</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.06779205977952785</v>
+        <v>-0.02441890833115679</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.09288513193680359</v>
+        <v>-0.05487773328132306</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3087075832401354</v>
+        <v>-0.2377118579805781</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5400455084887028</v>
+        <v>-0.4614953649874067</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7138590203106361</v>
+        <v>-0.6145588953438264</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.8848118513202152</v>
+        <v>-0.76138137632244</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.038249709233654</v>
+        <v>-0.9059514638913768</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.242950867493846</v>
+        <v>-1.126561334272857</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.151725632580799</v>
+        <v>-1.048219202614675</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.111466052578926</v>
+        <v>-1.003494431231289</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.8286517778933984</v>
+        <v>-0.7544495692159217</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2535</v>
+        <v>2538</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3165622988588694</v>
+        <v>0.336374237146785</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.151991800509137</v>
+        <v>-0.1655591378511687</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3594621890463117</v>
+        <v>0.4442108226640684</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.410885126172893</v>
+        <v>0.438454627133865</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.4636121215405495</v>
+        <v>0.5212839751651543</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2093707059431651</v>
+        <v>0.2651031981434997</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.1511473759392317</v>
+        <v>-0.0888080230467736</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.342408297109742</v>
+        <v>-0.2575756438452856</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5609948665560793</v>
+        <v>-0.452028567942719</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.7410949079607931</v>
+        <v>-0.6241497681471913</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.9851971694518795</v>
+        <v>-0.8676758005592191</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.7713630660390294</v>
+        <v>-0.6695179831447504</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.893619911551184</v>
+        <v>-0.7888681870923406</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.7247848144639804</v>
+        <v>-0.658026634769648</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2312</v>
+        <v>2315</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2130974560203143</v>
+        <v>-0.1414641074020579</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.4419941322374825</v>
+        <v>-0.4095319087502958</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3295411784718354</v>
+        <v>0.426766205090729</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.1573905121249908</v>
+        <v>0.1922318733444186</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.526228388834916</v>
+        <v>0.5893284505678622</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.2188507985995898</v>
+        <v>0.2818100075605727</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.2637300721627938</v>
+        <v>0.3506316913174174</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.160142027347483</v>
+        <v>-0.09145975030089204</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2643207281467213</v>
+        <v>-0.1716102523565084</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.63907753743554</v>
+        <v>-0.5397302121409666</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7141890628663603</v>
+        <v>-0.614281026847685</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6990197454550611</v>
+        <v>-0.5993108337592474</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.7060570894279721</v>
+        <v>-0.6056998618349638</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4128713264791628</v>
+        <v>-0.3566549998195967</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3662543763990129</v>
+        <v>-0.3056090106280678</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.2387186649515627</v>
+        <v>-0.1749407167063737</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.8702693487896411</v>
+        <v>0.9120341345063068</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.436584717941912</v>
+        <v>0.4573240287190501</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.6971673452973448</v>
+        <v>0.7457132650631166</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.4306316004963406</v>
+        <v>0.4545890094459537</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.5808836472452157</v>
+        <v>0.6288953262355363</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3487774094734988</v>
+        <v>0.3980249718672155</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1468178093417123</v>
+        <v>0.2200749191214086</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.5621235433791369</v>
+        <v>-0.4627762180845636</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.6728397392333036</v>
+        <v>-0.5729317032146284</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.8734239928930165</v>
+        <v>-0.7497273718647719</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.8706425153793589</v>
+        <v>-0.7219529676015313</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.7127112491735303</v>
+        <v>-0.6138855491951958</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1787949751799829</v>
+        <v>-0.1094923101735077</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.3414554603803879</v>
+        <v>-0.2709748604560644</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7640318201517005</v>
+        <v>0.810130724381473</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.1699941598083399</v>
+        <v>0.1930122617816394</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.006163991321493256</v>
+        <v>0.04238192844427857</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1743874784996535</v>
+        <v>-0.1504300695500405</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.1038986654947394</v>
+        <v>-0.0558869865044187</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.1571028498919276</v>
+        <v>-0.1078552874982108</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2475125103985363</v>
+        <v>0.3207696201782326</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.8093385156260879</v>
+        <v>-0.7099911903315146</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.065772731309977</v>
+        <v>-0.9658646952913017</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.548725153191597</v>
+        <v>-1.425028532163353</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.503278489691766</v>
+        <v>-1.354588941913939</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.352518285006809</v>
+        <v>-1.260743252169647</v>
       </c>
     </row>
     <row r="21">
@@ -2994,49 +2994,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.5865417481003661</v>
+        <v>-0.5330344609901303</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4755694025878441</v>
+        <v>-0.4235641394006322</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.6796018073758248</v>
+        <v>0.7051704625145234</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.7524216696783057</v>
+        <v>0.7519271773003027</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6733743668696377</v>
+        <v>0.7219202866354095</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.05226389593067893</v>
+        <v>0.076221304880292</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.08236409923626553</v>
+        <v>0.1303757782265862</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.07453770573655305</v>
+        <v>0.1237852681302698</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.4153925182149294</v>
+        <v>0.4886496279946257</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.008579090973718</v>
+        <v>-0.9092317656791451</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.098469686662156</v>
+        <v>-0.9985616506434809</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.925170753595005</v>
+        <v>-1.80147413256676</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.541647668906123</v>
+        <v>-1.392958121128295</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.571449600509311</v>
+        <v>-1.488344946828192</v>
       </c>
     </row>
     <row r="22">
@@ -3046,49 +3046,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6799992001479751</v>
+        <v>-0.6146869882856691</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3920366357134384</v>
+        <v>-0.3326610486955488</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.7849012133232733</v>
+        <v>0.814020222061302</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.7841505874289894</v>
+        <v>0.7836560950509863</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.9662277664878403</v>
+        <v>1.014773686253612</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4122592944857359</v>
+        <v>0.436216703435349</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.0001095115129459145</v>
+        <v>0.04812119050326658</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1395197085671711</v>
+        <v>-0.09027214617345436</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1350139803486243</v>
+        <v>-0.06175687056892798</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.9849327766784839</v>
+        <v>-0.8855854513839105</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.600242972266777</v>
+        <v>-0.5003349362481018</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.220743667324676</v>
+        <v>-1.097047046296431</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.7895520190008938</v>
+        <v>-0.6408624712230662</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.854864097683695</v>
+        <v>-0.7847449176556367</v>
       </c>
     </row>
     <row r="23">
@@ -3098,49 +3098,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.6096585455044092</v>
+        <v>-0.6388543398570405</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.6489883511430961</v>
+        <v>-0.6501751375877518</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.6777971503294182</v>
+        <v>0.6776437603250969</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.8080222939177801</v>
+        <v>0.8075278015397771</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3445830402232772</v>
+        <v>0.3931289599890491</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.04315467464878253</v>
+        <v>0.0671120835983956</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.4906574810245701</v>
+        <v>-0.4426458020342494</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5086243284041245</v>
+        <v>-0.4593767660104078</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.04565438911851061</v>
+        <v>0.02760272066118574</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.9704234848495688</v>
+        <v>-0.8710761595549954</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.351771349696584</v>
+        <v>-0.2518633136779087</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.140746490754438</v>
+        <v>-1.017049869726193</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5878434518522795</v>
+        <v>-0.4391539040744519</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.9942704426358588</v>
+        <v>-0.9386120360710635</v>
       </c>
     </row>
     <row r="24">
@@ -3150,49 +3150,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.324103691202737</v>
+        <v>-1.353299485555368</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.050114120170591</v>
+        <v>-1.051300906615246</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.783049370824159</v>
+        <v>0.7828959808198377</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.084654120239428</v>
+        <v>1.084159627861425</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.8034339758840972</v>
+        <v>0.851979895649869</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.5009793851250066</v>
+        <v>0.5249367940746197</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.183559594535339</v>
+        <v>-0.1355479155450183</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.3935588295817141</v>
+        <v>-0.3443112671879973</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.4023570430300367</v>
+        <v>0.4756141528097331</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.8760107678670863</v>
+        <v>-0.776663442572513</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.05243429116583798</v>
+        <v>0.04747374485283729</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.217713379598862</v>
+        <v>-1.094016758570618</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8666560066911941</v>
+        <v>-0.7179664589133665</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.107657867874039</v>
+        <v>-0.9830604143787127</v>
       </c>
     </row>
     <row r="25">
@@ -3202,49 +3202,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.0610377343883</v>
+        <v>-1.090233528740931</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2381467483446329</v>
+        <v>-0.2393335347892886</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.003998702600128</v>
+        <v>2.003845312595807</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.627124454707761</v>
+        <v>1.626629962329758</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.393094536500506</v>
+        <v>1.441640456266278</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.9805294180625665</v>
+        <v>1.00448682701218</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.1858799107233793</v>
+        <v>0.2338915897136999</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4287504150096595</v>
+        <v>0.4779979774033762</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.381967041448348</v>
+        <v>1.455224151228045</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.4821505378429762</v>
+        <v>-0.3828032125484029</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.3273470868582962</v>
+        <v>0.4272551228769714</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.260992813524716</v>
+        <v>-1.137296192496471</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.7683647621728156</v>
+        <v>-0.619675214394988</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.399601342462852</v>
+        <v>-1.28340925704493</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>828</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.877051296234832</v>
+        <v>-1.906247090587463</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.01417806963853252</v>
+        <v>0.01299128319387677</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.672546781501858</v>
+        <v>1.672393391497536</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.681998978230318</v>
+        <v>1.681504485852315</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.713757734313361</v>
+        <v>2.762303654079133</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.441083454769711</v>
+        <v>1.465040863719324</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.3901895206243111</v>
+        <v>0.4382011996146318</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.1646667705573748</v>
+        <v>0.2139143329510915</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.190641135773724</v>
+        <v>1.26389824555342</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.1423694479957405</v>
+        <v>-0.04302212270116712</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2567941280435804</v>
+        <v>0.3567021640622556</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.9165571882001302</v>
+        <v>-0.7928605671718856</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1125673208052973</v>
+        <v>0.2612568685831249</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.1447888164077824</v>
+        <v>0.02720994315887992</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>721</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.134175392531581</v>
+        <v>-2.163371186884213</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2779551055676706</v>
+        <v>-0.2791418920123263</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.407717337693931</v>
+        <v>1.40756394768961</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.537942481282293</v>
+        <v>1.53744798890429</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.080096756203247</v>
+        <v>3.128642675969019</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.574419468223908</v>
+        <v>1.598376877173521</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.380139067348864</v>
+        <v>0.4281507463391847</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.2256258316389861</v>
+        <v>-0.1763782692452693</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.6842657982460025</v>
+        <v>0.7575229080256989</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4430455084860725</v>
+        <v>-0.3436981831914991</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.0457346092592843</v>
+        <v>0.1456426452779596</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.584242300798707</v>
+        <v>-1.460545679770462</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4787343468999126</v>
+        <v>-0.330044799122085</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.5303912070756027</v>
+        <v>-0.3583924475089404</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>578</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.096832985551657</v>
+        <v>-1.126028779904289</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.9779152723871078</v>
+        <v>-0.9791020588317636</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.7034379103318997</v>
+        <v>0.7032845203275784</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.487642292674586</v>
+        <v>0.487147800296583</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.852466926430111</v>
+        <v>1.901012846195883</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.2723043726545313</v>
+        <v>-0.2483469637049183</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.568087396280561</v>
+        <v>-1.52007571729024</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.51612489819879</v>
+        <v>-1.466877335805073</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.4990175127524807</v>
+        <v>0.5722746225321771</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.6969220448230473</v>
+        <v>-0.597574719528474</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.2095816805918886</v>
+        <v>-0.1096736445732134</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.559286573219261</v>
+        <v>-1.435589952191016</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.5953543815499742</v>
+        <v>-0.4466648337721466</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.149412410545068</v>
+        <v>0.3214111701117304</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>458</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.389212973765794</v>
+        <v>-1.418408768118425</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.782058455475905</v>
+        <v>-2.783245241920561</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.866786172108682</v>
+        <v>-1.866939562113004</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.2998798058129</v>
+        <v>-1.300374298190903</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.000258588689661</v>
+        <v>1.048804508455433</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.32245471791979</v>
+        <v>-1.298497308970177</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.717208745308227</v>
+        <v>-2.669197066317906</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.310914943680118</v>
+        <v>-2.261667381286401</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.2481902360416441</v>
+        <v>0.3214473458213405</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.1650473375807948</v>
+        <v>-0.06570001228622147</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1514078844872699</v>
+        <v>-0.05149984846859468</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.645414011607926</v>
+        <v>-1.521717390579681</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.5371805854453555</v>
+        <v>-0.3884910376675279</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.0931043238651128</v>
+        <v>0.07889443570154953</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>382</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1248950881259745</v>
+        <v>-0.1540908824786058</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.259641390613886</v>
+        <v>-2.260828177058542</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-2.91619288008097</v>
+        <v>-2.916346270085292</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.215287108220352</v>
+        <v>-1.215781600598355</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.07888407166824152</v>
+        <v>0.1274299914340133</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.241542945817088</v>
+        <v>-2.217585536867475</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-3.373373723931422</v>
+        <v>-3.325362044941102</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.269761739445919</v>
+        <v>-2.220514177052202</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.07239746528785</v>
+        <v>1.145654575067546</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.301081540466086</v>
+        <v>-0.2017342151715127</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5057826987262786</v>
+        <v>-0.4058746627076033</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.256744860507084</v>
+        <v>-1.133048239478839</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.8915553996843641</v>
+        <v>-0.7428658519065365</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6658197494578317</v>
+        <v>-0.4938209898911694</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>299</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.6414511475912121</v>
+        <v>-0.6706469419438434</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-3.924878043330622</v>
+        <v>-3.926064829775278</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.312960464874962</v>
+        <v>-2.313113854879283</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.4928499629943346</v>
+        <v>0.4923554706163316</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.961249373109339</v>
+        <v>2.009795292875111</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4169618815365084</v>
+        <v>-0.3930044725868953</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.83946488294314</v>
+        <v>-1.79145320395282</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.972085366194761</v>
+        <v>-1.922837803801045</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.649206724774096</v>
+        <v>2.722463834553793</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.130391607374001</v>
+        <v>1.229738932668575</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.263483091254287</v>
+        <v>2.363391127272962</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.29451676200425</v>
+        <v>1.418213383032494</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.2054695876206054</v>
+        <v>0.354159135398433</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.434549719452491</v>
+        <v>1.606548479019153</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>229</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.825894196473222</v>
+        <v>-1.855089990825853</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-6.493848848489009</v>
+        <v>-6.495035634933664</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.26853289699951</v>
+        <v>-4.268686287003831</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.518220417166603</v>
+        <v>-1.518714909544606</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.436939811397089</v>
+        <v>1.485485731162861</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.75913594062721</v>
+        <v>-1.735178531677597</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.843846299893379</v>
+        <v>-1.795834620903058</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.874233720972697</v>
+        <v>-1.82498615857898</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.431596349578768</v>
+        <v>2.504853459358465</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.01835877595633</v>
+        <v>2.117706101250903</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.687020063110985</v>
+        <v>2.786928099129661</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.41135454734404</v>
+        <v>1.535051168372284</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1178412486157754</v>
+        <v>0.266530796393603</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.653620566964584</v>
+        <v>1.825619326531246</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>174</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-1.33149074317803</v>
+        <v>-1.360686537530661</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-3.337448220996897</v>
+        <v>-3.337601611001219</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.05779779005222</v>
+        <v>-2.058292282430223</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2972367684352619</v>
+        <v>-0.2486908486694901</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.5745753824783364</v>
+        <v>-0.5506179735287233</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.4901395456118109</v>
+        <v>0.5381512246021316</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.172496189181395</v>
+        <v>1.221743751575112</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>5.134502538405748</v>
+        <v>5.207759648185444</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.85929638575405</v>
+        <v>4.958643711048623</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.378733158528334</v>
+        <v>6.478641194547009</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.815410161458374</v>
+        <v>1.939106782486618</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2458340207886494</v>
+        <v>0.394523568566477</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>2.77042024572782</v>
+        <v>2.942419005294482</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>135</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-4.332767882386207</v>
+        <v>-4.361963676738839</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-5.203213234709295</v>
+        <v>-5.204400021153951</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.857243878723594</v>
+        <v>-4.857397268727915</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-3.986277994394491</v>
+        <v>-3.986772486772495</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.524567547490186</v>
+        <v>-4.476021627724414</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-2.745712036373618</v>
+        <v>-2.721754627424005</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.348940914158298</v>
+        <v>-1.300929235167978</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-1.816009557945037</v>
+        <v>-1.76676199555132</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2.567452729976623</v>
+        <v>2.640709839756319</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.458274674387503</v>
+        <v>2.557621999682077</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.994314256868051</v>
+        <v>3.094222292886727</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-2.156492775961802</v>
+        <v>-2.032796154933557</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-4.058125110756698</v>
+        <v>-3.909435562978871</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.869426497567197</v>
+        <v>-0.6974277380005347</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-6.052344601962922</v>
+        <v>-6.081540396315553</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-5.282578314074371</v>
+        <v>-5.283765100519027</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-3.29639731787703</v>
+        <v>-3.296550707881352</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-1.975695983812471</v>
+        <v>-1.976190476190474</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-6.085414108336742</v>
+        <v>-6.036868188570971</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.35481706415549</v>
+        <v>1.378774473105103</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.110845676063065</v>
+        <v>-1.062833997072744</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-1.63889647637258</v>
+        <v>-1.565639366592883</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-3.679291463178622</v>
+        <v>-3.579944137884048</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-2.693516430962632</v>
+        <v>-2.593608394943956</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-10.99247161194064</v>
+        <v>-10.86877499091239</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-14.98405103668262</v>
+        <v>-14.83536148890479</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-8.805934434075141</v>
+        <v>-8.633935674508479</v>
       </c>
     </row>
   </sheetData>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3.471464921846604</v>
+        <v>3.442269127493972</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2750312535515462</v>
+        <v>0.2748778635472249</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.595732587616098</v>
+        <v>1.595238095238095</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.438395415472783</v>
+        <v>3.486941335238555</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1643408736793006</v>
+        <v>0.1882982826289137</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.0796305144131324</v>
+        <v>0.1276421934034531</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.8030380611025834</v>
+        <v>0.8522856234963001</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4.313484476008377</v>
+        <v>4.386741585788073</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.034994251107086</v>
+        <v>7.13434157640166</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.020769283323091</v>
+        <v>8.120677319341766</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.245623626154604</v>
+        <v>9.369320247182849</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.20642515379357</v>
+        <v>11.3551147015714</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>141</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2.12901304747983</v>
+        <v>2.099817253127199</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.610025535976284</v>
+        <v>7.608838749531628</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.669154860441104</v>
+        <v>3.669001470436783</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.636259436653582</v>
+        <v>6.635764944275579</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.225629458025978</v>
+        <v>8.274175377791749</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.104563771349</v>
+        <v>7.128521180298613</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.147512986550922</v>
+        <v>9.195524665541242</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.389664200920215</v>
+        <v>9.438911763313932</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.03790190255347</v>
+        <v>10.11115901233317</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.89720296437963</v>
+        <v>9.996550289674204</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.11094152243149</v>
+        <v>11.21084955845016</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>12.56375939109888</v>
+        <v>12.68745601212712</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>13.56204825409752</v>
+        <v>13.71073780187535</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>13.78778390432405</v>
+        <v>13.95978266389071</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>209</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.107600715877133</v>
+        <v>1.078404921524502</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>7.63038591467933</v>
+        <v>7.629199128234674</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.843270032316632</v>
+        <v>4.84311664231231</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.887370773991123</v>
+        <v>6.886876281613119</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.306019019938496</v>
+        <v>7.354564939704268</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.603393049573583</v>
+        <v>7.627350458523196</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.82490278600119</v>
+        <v>11.87291446499151</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>11.35783414221445</v>
+        <v>11.40708170460817</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>11.7753208852132</v>
+        <v>11.8485779949929</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>11.40387098840488</v>
+        <v>11.50321831369945</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>11.67763872966621</v>
+        <v>11.77754676568489</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>14.58283027915073</v>
+        <v>14.70652690017898</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>13.68421052631578</v>
+        <v>13.83290007409361</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>13.43147727702078</v>
+        <v>13.60347603658744</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>297</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.975865525483847</v>
+        <v>-2.005061319836479</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.157056125560068</v>
+        <v>4.155869339115412</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.425584404104697</v>
+        <v>3.425431014100376</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.912711904595412</v>
+        <v>5.912217412217409</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.72122369830106</v>
+        <v>6.769769618066832</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.345197054535475</v>
+        <v>6.369154463485089</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8.954089388871999</v>
+        <v>9.00210106786232</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.476919734984257</v>
+        <v>7.526167297377974</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.415937578461481</v>
+        <v>7.489194688241177</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.912820128932964</v>
+        <v>8.012167454227537</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.708118970672771</v>
+        <v>7.808027006691447</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9.762699143230115</v>
+        <v>9.88639576425836</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.985645933014347</v>
+        <v>7.134335480792174</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.211381583240879</v>
+        <v>7.383380342807541</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>400</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.7309160305343596</v>
+        <v>-0.7601118248869909</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4.907897876401819</v>
+        <v>4.906711089957163</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.013126491646773</v>
+        <v>3.012973101642451</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.643351635235142</v>
+        <v>4.642857142857139</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.855062082139455</v>
+        <v>5.903608001905226</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.652436111774541</v>
+        <v>6.676393520724154</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.317725752508366</v>
+        <v>7.365737431498687</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.600657108721634</v>
+        <v>6.649904671115351</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.289674952198851</v>
+        <v>7.362932061978547</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.939756155868992</v>
+        <v>8.039103481163565</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.735054997608799</v>
+        <v>7.834963033627474</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>7.769433149964122</v>
+        <v>7.893129770992367</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.849282296650713</v>
+        <v>6.997971844428541</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.825017946877239</v>
+        <v>6.997016706443901</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>504</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2983763479946688</v>
+        <v>-0.3275721423473001</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.431707400211344</v>
+        <v>5.430520613766689</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.052809031329318</v>
+        <v>3.052655641324996</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4.770335762219268</v>
+        <v>4.769841269841265</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.422522399599764</v>
+        <v>5.471068319365536</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.315134524472938</v>
+        <v>6.339091933422552</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>6.032011466794074</v>
+        <v>6.080023145784395</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5.564942823007335</v>
+        <v>5.614190385401052</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.702373364897255</v>
+        <v>5.775630474676952</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>6.836581552694383</v>
+        <v>6.935928877988957</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>7.02870579125959</v>
+        <v>7.128613827278265</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.467845848376818</v>
+        <v>6.591542469405063</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.452456899825322</v>
+        <v>5.601146447603149</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.68612905798836</v>
+        <v>4.858127817555022</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.3404005838857174</v>
+        <v>0.3112047895330861</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.901628283925334</v>
+        <v>3.900441497480678</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.185026020689172</v>
+        <v>2.096045201955938</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.504986855360926</v>
+        <v>3.323107926556197</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.224558937485355</v>
+        <v>4.087777280902081</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.207467558315415</v>
+        <v>4.047083175896553</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.965524494646736</v>
+        <v>3.829687274758875</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.127386668470059</v>
+        <v>3.990813762024437</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.104635582120103</v>
+        <v>4.894280024360988</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.357078990514665</v>
+        <v>5.167630126931584</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>5.939779407057621</v>
+        <v>5.747188738956623</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.871795354688537</v>
+        <v>4.708176792935937</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.609124816335751</v>
+        <v>4.469758678284343</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.047458891759135</v>
+        <v>4.029591274732759</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.08827799372453882</v>
+        <v>-0.1174737880771701</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2.349615667812856</v>
+        <v>2.3484288813682</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.024183002703289</v>
+        <v>1.954690893053495</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.469919900917795</v>
+        <v>2.329973707274313</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.98683548115423</v>
+        <v>2.822319658346935</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.0379040920701</v>
+        <v>2.849706404159733</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.024260894308611</v>
+        <v>2.789050314934272</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.803801375059479</v>
+        <v>2.568616327557059</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.295847791705029</v>
+        <v>4.004036356457078</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.310126526239365</v>
+        <v>4.039103481163565</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4.846166108719913</v>
+        <v>4.571159352645886</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.263260310457952</v>
+        <v>4.015829157495432</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.213479827514909</v>
+        <v>3.988769390440808</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.698474737000701</v>
+        <v>3.575026534453741</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.5277910305343525</v>
+        <v>-0.5569868248869838</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.474304126401819</v>
+        <v>1.473117339957163</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.524856696925369</v>
+        <v>1.470004351642459</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.709887838757652</v>
+        <v>1.599888392857139</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.695659535616436</v>
+        <v>2.575483001905219</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.147534150990218</v>
+        <v>2.945924770724147</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.217627617081476</v>
+        <v>2.982924931498687</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.848694400183852</v>
+        <v>2.614748421115344</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.023466700725372</v>
+        <v>3.749650811978547</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.254098002627337</v>
+        <v>4.000040981163565</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.933483288375001</v>
+        <v>4.674806783627474</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.083774996722468</v>
+        <v>3.854067270992367</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.663624143409059</v>
+        <v>3.458909344428541</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.005273349627736</v>
+        <v>2.886801652680468</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1694805074199977</v>
+        <v>-0.198676301772629</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.9768354270911956</v>
+        <v>0.9756486406465399</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.19494467346496</v>
+        <v>1.149631658009042</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.370402813139286</v>
+        <v>1.279515699223722</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.527826309781723</v>
+        <v>1.439090564760043</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.871109830244833</v>
+        <v>1.711876083578971</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.402416306254295</v>
+        <v>2.218941000030725</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.470869007662138</v>
+        <v>2.239726244513562</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.354112146326088</v>
+        <v>3.094886644298093</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3.449960237501649</v>
+        <v>3.163191072404445</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.029172644667618</v>
+        <v>3.688977632167628</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>3.736753411402027</v>
+        <v>3.422732366288393</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.908105826062474</v>
+        <v>2.622059435669421</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.480246705047179</v>
+        <v>2.269743979171182</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1433</v>
+        <v>1441</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.5058640554823768</v>
+        <v>-0.5710536531418242</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1392588503665593</v>
+        <v>-0.1459204889902068</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5659852363199107</v>
+        <v>-0.6781626324295615</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.1572405241240276</v>
+        <v>0.07499010684605878</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2127757722019936</v>
+        <v>0.1397575863927543</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.6875543315241828</v>
+        <v>0.5510472603363326</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.19803194596696</v>
+        <v>1.044407791609494</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.4662559945155</v>
+        <v>1.271095806849409</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>1.688988888035375</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.238221985715569</v>
+        <v>1.973961416021496</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.562689331174745</v>
+        <v>2.324221522885964</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.387716471666849</v>
+        <v>2.174488052350654</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.316483971458801</v>
+        <v>2.097139666897327</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.774599244853526</v>
+        <v>1.623491376811714</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1623</v>
+        <v>1631</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4907139484767953</v>
+        <v>-0.5223442407891312</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3809370920880895</v>
+        <v>0.402123933993856</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.5935565249074841</v>
+        <v>-0.725559008449288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.6143170764213011</v>
+        <v>-0.6568370467453093</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.6899041548157427</v>
+        <v>-0.7791137106330055</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2363845270461056</v>
+        <v>-0.3228419532819657</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3884079897548389</v>
+        <v>0.2892848321103045</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.631714919299732</v>
+        <v>0.4962349463446998</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.097367259891158</v>
+        <v>0.9216835919663069</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.390495072125155</v>
+        <v>1.199446198421825</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.714106137473244</v>
+        <v>1.52020491972668</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.378798522730605</v>
+        <v>1.210949734250178</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.574790614580479</v>
+        <v>1.402383609134425</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.307611908676385</v>
+        <v>1.196434241698348</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1846</v>
+        <v>1854</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2669287970518539</v>
+        <v>0.1780602181237683</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.6787873642724378</v>
+        <v>0.6378938856560907</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.4415660649875193</v>
+        <v>-0.562295715561838</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1742414570476427</v>
+        <v>-0.2173579109063013</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6292791705603378</v>
+        <v>-0.7066070518582208</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1945384965452917</v>
+        <v>-0.2725312104586521</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.1957877610051497</v>
+        <v>-0.3039774689854369</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.2860275792462303</v>
+        <v>0.1984522773552584</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5256056881295876</v>
+        <v>0.4065273257029816</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.005267796367093</v>
+        <v>0.874410262649036</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.048164423394276</v>
+        <v>0.9162769808541853</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.02837139481786</v>
+        <v>0.8974401158199612</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.0415899889584</v>
+        <v>0.9103707662614298</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.671442648935745</v>
+        <v>0.597070643876485</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2031</v>
+        <v>2041</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3825200928136638</v>
+        <v>0.319156467795942</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.364313155539925</v>
+        <v>0.2969549923961878</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9346932045805616</v>
+        <v>-0.9748317764063188</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4350797373138775</v>
+        <v>-0.4547038327526138</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.7017059414015065</v>
+        <v>-0.748831022485021</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3777405319938651</v>
+        <v>-0.4008392757619461</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4849252047817671</v>
+        <v>-0.5327000685013132</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.286867449235146</v>
+        <v>-0.3370274246345346</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.02309018561408038</v>
+        <v>-0.05397898396476108</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.7735811312868819</v>
+        <v>0.6650203515792157</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.8427775750805182</v>
+        <v>0.7332017811812932</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.052897716893256</v>
+        <v>0.9171141077520346</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.054846058344459</v>
+        <v>0.8926829120093487</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.8866870753853675</v>
+        <v>0.7778839283939263</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2226</v>
+        <v>2236</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.1553663644611873</v>
+        <v>0.09567882099275238</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.4005219264688691</v>
+        <v>0.3387823594449131</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6854423813406996</v>
+        <v>-0.7231070765312637</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.1284604453017693</v>
+        <v>-0.1477887368755972</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.02896539458349423</v>
+        <v>-0.01342986001014879</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.2165874776500445</v>
+        <v>0.1946644654656851</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.2012382973112352</v>
+        <v>0.1584257952971697</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2069995560546545</v>
+        <v>0.1630625658521936</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.05337437515540699</v>
+        <v>-0.1169876167363171</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.8711155098393846</v>
+        <v>0.7801749097349955</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.051033453623162</v>
+        <v>0.958678978245608</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.470376122573015</v>
+        <v>1.355149431403447</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.435535665922949</v>
+        <v>1.298597682604672</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.301882277515162</v>
+        <v>1.215710803044978</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2417</v>
+        <v>2427</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4215129525862764</v>
+        <v>0.3827892830325936</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.4383756358746353</v>
+        <v>0.3999404703428837</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.5107713245872603</v>
+        <v>-0.5272402754605423</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.5231776310467993</v>
+        <v>-0.5204584090509385</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4619482271389046</v>
+        <v>-0.4949962673887072</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.02289815797915651</v>
+        <v>0.005448962202585506</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.04327259526527882</v>
+        <v>0.008301112681927236</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.01168105587273516</v>
+        <v>-0.02405751548556623</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.1504324414401452</v>
+        <v>-0.202857411705665</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8819049161995736</v>
+        <v>0.8058661302791492</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.9074402807836606</v>
+        <v>0.8308478072900272</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.503097335241215</v>
+        <v>1.406509762758525</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.230953790237805</v>
+        <v>1.117411712632823</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.249821422259956</v>
+        <v>1.184181931000971</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2632</v>
+        <v>2642</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.3935166472266118</v>
+        <v>0.3556498644041213</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.3157677212750656</v>
+        <v>0.2807684051909476</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4747614720171072</v>
+        <v>-0.4900434896094268</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4376782776766319</v>
+        <v>-0.4355742296918805</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.5388773117999435</v>
+        <v>-0.5649887540359373</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1830129219503647</v>
+        <v>-0.1962479887098141</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.09407146896022311</v>
+        <v>0.06562418121556135</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.1407594978001256</v>
+        <v>0.1113850336531144</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.2145611433976384</v>
+        <v>0.1708277929947926</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.7139497042560876</v>
+        <v>0.6528600949201788</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4548727652625573</v>
+        <v>0.3945093474270962</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.8146287443431603</v>
+        <v>0.7388181219757257</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.568127281453144</v>
+        <v>0.478675590172017</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.6038933268164612</v>
+        <v>0.5600371455052198</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2823</v>
+        <v>2833</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.2880434050917557</v>
+        <v>0.3008509298565087</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.3891963943975867</v>
+        <v>0.3882576628921299</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3393267381449689</v>
+        <v>-0.3379411037021285</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.3665353704145744</v>
+        <v>-0.3648811617506666</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1439665296584991</v>
+        <v>-0.1665890424297558</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.03141137679219952</v>
+        <v>0.01984653022784499</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.319493161486804</v>
+        <v>0.2953148962874224</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2962016631770794</v>
+        <v>0.2715143928483528</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1487128015090704</v>
+        <v>0.113108242387284</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5922685408654473</v>
+        <v>0.542452088847746</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2660284489362397</v>
+        <v>0.2171915244596292</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.6391215352332438</v>
+        <v>0.5774331219623861</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.3808090412486607</v>
+        <v>0.3081341591780102</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.5711213829381734</v>
+        <v>0.5419337555085022</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2992</v>
+        <v>3002</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.5150892956973365</v>
+        <v>0.5247140457597794</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.4866524551563955</v>
+        <v>0.4853441357434889</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.3229827688462308</v>
+        <v>-0.3217431280289631</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.4079645926888773</v>
+        <v>-0.4062796433314446</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2949379178605511</v>
+        <v>-0.3130143826846208</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1460800602828201</v>
+        <v>-0.1550018281130576</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1542834576451213</v>
+        <v>0.1347636860683039</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.2060124640769772</v>
+        <v>0.1858089264344969</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.03676029479714771</v>
+        <v>-0.06556810430013371</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.4673020657187408</v>
+        <v>0.4263290300657658</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1144805153108734</v>
+        <v>0.07456369918487127</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.5686312789317114</v>
+        <v>0.5176304367713342</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.4348437939769099</v>
+        <v>0.3744287208854118</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.5268896046312506</v>
+        <v>0.4758641414872145</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3173</v>
+        <v>3183</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.3291310652270312</v>
+        <v>0.3371973115335436</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.1478476251455376</v>
+        <v>0.1477126549023851</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6383029774075695</v>
+        <v>-0.6360563285391265</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4911549643877393</v>
+        <v>-0.4893069661312808</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4152145604257811</v>
+        <v>-0.4290987650120712</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2579412467160296</v>
+        <v>-0.2646124335221742</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.02046246216549719</v>
+        <v>0.005235864100569643</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.08326359612419054</v>
+        <v>-0.09852743926408181</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.3157704365326595</v>
+        <v>-0.3378207611080271</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.2684715211082818</v>
+        <v>0.2361539988918366</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.01297649845419357</v>
+        <v>-0.04450965940454665</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.4802081972230994</v>
+        <v>0.4394406030174807</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.3300575881729344</v>
+        <v>0.2818914424184911</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.5242773228621189</v>
+        <v>0.4859422483854701</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3330</v>
+        <v>3341</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.4655392491545456</v>
+        <v>0.4714027845346038</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.06708399249996688</v>
+        <v>0.06716441533741602</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4312015538485809</v>
+        <v>-0.4297476620806933</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.404552556381617</v>
+        <v>-0.4030992880590105</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6571421706308413</v>
+        <v>-0.6672875204828443</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3135614915807707</v>
+        <v>-0.3186049862928755</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.02240010904392875</v>
+        <v>-0.03450151712736016</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.006532408481817242</v>
+        <v>-0.005981196826098767</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1878362921789574</v>
+        <v>-0.2058067306096234</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1485144042193269</v>
+        <v>0.1228105065746234</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.02068356046508057</v>
+        <v>-0.004749885032815371</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.3120501967828559</v>
+        <v>0.2796089812825286</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.05897908440213939</v>
+        <v>0.02101194017958363</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.1215644934237972</v>
+        <v>0.07745669447144365</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3437</v>
+        <v>3448</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4466202013497025</v>
+        <v>0.4514599751707991</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1265119674427027</v>
+        <v>0.1263642691479134</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3105394016246805</v>
+        <v>-0.3095189480828893</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3096509757309107</v>
+        <v>-0.3085598611914406</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6291224796713522</v>
+        <v>-0.6375403926565326</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.2869688229134155</v>
+        <v>-0.2911990718684478</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.007477499524156883</v>
+        <v>-0.01776473926832267</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.09317816593917172</v>
+        <v>0.08230189172912361</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.03891307801613664</v>
+        <v>-0.05453101360789958</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.2024704830994466</v>
+        <v>0.1804708044544157</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.07226429993438188</v>
+        <v>0.05055271777700199</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.4138065143142171</v>
+        <v>0.3858833941807731</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.1846516974651422</v>
+        <v>0.1520744828744682</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1941625497285671</v>
+        <v>0.156529467464793</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3580</v>
+        <v>3591</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1770299755886597</v>
+        <v>0.1813421151796035</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.2230426425488119</v>
+        <v>0.2225589944811688</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1287559923409702</v>
+        <v>-0.1283372814780321</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.06695477145009932</v>
+        <v>-0.06666798905066429</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2836255745894505</v>
+        <v>-0.2908364425392236</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.08471035926616821</v>
+        <v>0.08046409588391157</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.3219075200020995</v>
+        <v>0.3129303164347661</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2884708287439395</v>
+        <v>0.2793875735340308</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.01980047521140449</v>
+        <v>0.007537178774988718</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2176579415832833</v>
+        <v>0.2004386689243418</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1123924243461687</v>
+        <v>0.09539709038874378</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3300138311478165</v>
+        <v>0.3083816496453053</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.1769840559358329</v>
+        <v>0.1516466773906799</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.05546487425154822</v>
+        <v>0.02660456497913799</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3700</v>
+        <v>3711</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1719253376315493</v>
+        <v>0.1751728152848742</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.4068202901949221</v>
+        <v>0.4057709878889426</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.2153630855567741</v>
+        <v>0.2147463418358981</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1716535220275901</v>
+        <v>0.1712097362460128</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.1092814066715562</v>
+        <v>-0.1152092023958531</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2028676112351562</v>
+        <v>0.1991819046983352</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.4027001253165707</v>
+        <v>0.3953232303152561</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.3282609943125578</v>
+        <v>0.3209431430012728</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.06632812358886042</v>
+        <v>0.05668878964270618</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.1222615554370279</v>
+        <v>0.1090900222133655</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.09476334219426974</v>
+        <v>0.08159739011642841</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.2794277474789766</v>
+        <v>0.2626422945582121</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.1447429829517191</v>
+        <v>0.1251270168423346</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.08853146039076165</v>
+        <v>0.06606817505074503</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3776</v>
+        <v>3787</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.01314572718536056</v>
+        <v>0.01620396458670115</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.2901576440892555</v>
+        <v>0.2894433879303122</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2794322745884159</v>
+        <v>0.2786392417161778</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.13357878790287</v>
+        <v>0.1332442906053615</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.005986784913559973</v>
+        <v>0.0008155888388330368</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2650153929584675</v>
+        <v>0.26170313864246</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.4062798101345919</v>
+        <v>0.4000020598592613</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2710695888908532</v>
+        <v>0.2650509932877654</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.01328722711878783</v>
+        <v>-0.02103418274718649</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.1302323463451813</v>
+        <v>0.1192934046665997</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.1256345159999057</v>
+        <v>0.1146464109361816</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2014077396941403</v>
+        <v>0.1876665880945012</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1668623866692514</v>
+        <v>0.1505589616407903</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.1428145570467407</v>
+        <v>0.1240961888838399</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3859</v>
+        <v>3870</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.05007570500283975</v>
+        <v>0.0523398877063741</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.3641107412946099</v>
+        <v>0.3631768292667985</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.1642892823444484</v>
+        <v>0.1638362812353478</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.02736431203805978</v>
+        <v>-0.02724594992636753</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1379575662576613</v>
+        <v>-0.1415711679839262</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.07013717202796244</v>
+        <v>0.06796133918727065</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.2064996790474254</v>
+        <v>0.2019509986898171</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1934772898341777</v>
+        <v>0.1888623594538359</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.1119813625009414</v>
+        <v>-0.1177130993117785</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.01016775307324025</v>
+        <v>0.001932598355104176</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1023349557832276</v>
+        <v>-0.1102990371187218</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.0275106469796782</v>
+        <v>-0.0376553529745749</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.05912685623619751</v>
+        <v>0.04666727196664766</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.03731685488486391</v>
+        <v>-0.05143290595919581</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3929</v>
+        <v>3940</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1066029953408432</v>
+        <v>0.1081527842706222</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.4372051588174486</v>
+        <v>0.4360633166778172</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2339386743879004</v>
+        <v>0.2332970702579971</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.09879717978959945</v>
+        <v>0.09855334538878679</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.07015376346745938</v>
+        <v>-0.07303165370379361</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1395455859934813</v>
+        <v>0.1376397213320502</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1703680289311365</v>
+        <v>0.1668522022106202</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.1492593958880803</v>
+        <v>0.1457232215461559</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.05018269904670092</v>
+        <v>-0.05468517503032189</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.02159650113583211</v>
+        <v>-0.02783363851188625</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.08488396475132021</v>
+        <v>-0.09098167852064165</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.01077544835691668</v>
+        <v>-0.01859016812483105</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.06683954855911622</v>
+        <v>0.05722076602204851</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.02386217529124934</v>
+        <v>-0.03470918188096306</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3984</v>
+        <v>3995</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.05848852288070816</v>
+        <v>0.05974845455413202</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.237227205731152</v>
+        <v>0.2366337253452357</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.131399332698102</v>
+        <v>0.1310459923064613</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1000366627764464</v>
+        <v>0.09978598180845211</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.0261740280447782</v>
+        <v>0.02373787203509181</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.06175474904907929</v>
+        <v>0.0604180023629155</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.04085278833898798</v>
+        <v>0.03840109966461114</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.01149827974955286</v>
+        <v>-0.01386688599538388</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1338647820703827</v>
+        <v>-0.1370679380214455</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1174153586746414</v>
+        <v>-0.1219367789014569</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2077591483656178</v>
+        <v>-0.2120604781284072</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.008790633277222071</v>
+        <v>-0.01480117721879282</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.06195481860805785</v>
+        <v>0.05452840098509881</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.04948004509062542</v>
+        <v>-0.05773923848725104</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4023</v>
+        <v>4034</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1454467048472168</v>
+        <v>0.1461767839590706</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.2325571081242472</v>
+        <v>0.2319706055280975</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1487239135605094</v>
+        <v>0.1483253884162536</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1437235667997356</v>
+        <v>0.1433517026988795</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1645858916632577</v>
+        <v>0.1622649398226059</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1283105846100554</v>
+        <v>0.1270367666420071</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.106807638364451</v>
+        <v>0.1046634399124429</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1000986574930351</v>
+        <v>0.09792447309554575</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.003180413966482831</v>
+        <v>0.0003423120404377755</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.01127341437408091</v>
+        <v>0.007404620341375789</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.03046909578414869</v>
+        <v>-0.03424677563683787</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1421039574175396</v>
+        <v>0.1369355192579746</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.2081292151397847</v>
+        <v>0.201813232284799</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.09999930407337132</v>
+        <v>0.09307520917073475</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4074</v>
+        <v>4085</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1249073117705137</v>
+        <v>0.1253200931217933</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1663413418937409</v>
+        <v>0.1659251490247726</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.05413016361740119</v>
+        <v>0.05398872664245857</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.05079531789920111</v>
+        <v>0.05067155067154516</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1381260057250486</v>
+        <v>0.136509809428432</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.008021609079776226</v>
+        <v>0.007385458178340798</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.08371448076124466</v>
+        <v>0.08225747059936594</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1447747557804533</v>
+        <v>0.1431214885194052</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1218642142728896</v>
+        <v>0.119655778359963</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.168299559498216</v>
+        <v>0.1652957042009859</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1245570824751283</v>
+        <v>0.1216557929229722</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2954390380897394</v>
+        <v>0.2914659589052562</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.3799571432764779</v>
+        <v>0.3751133030677991</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.2515029738777343</v>
+        <v>0.2464047113398635</v>
       </c>
     </row>
   </sheetData>
